--- a/doc/excel/認証タスク.xlsx
+++ b/doc/excel/認証タスク.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/suepie/Develop/10_project/aws-atuh-poc/doc/excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58899D08-1EB6-C445-9158-E3D9CBDD75A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E580E23E-6512-614D-ABF1-873A9A5D7E47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="780" windowWidth="34200" windowHeight="21460" activeTab="1" xr2:uid="{B021B529-7D79-6D49-8055-5FE1DF3A55F9}"/>
   </bookViews>
@@ -7346,10 +7346,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>アプリ認証方式の段階昇格を決定（第1段階=送信型の秘密情報／第2段階=鍵ペア方式へ一括昇格／第3段階=相互証明書方式は金融要件発生時のみ）。★要件文の意図確認が必要: 「アプリの身元証明」の意味なら段階決定済み、「利用者本人の証明書ログイン」の意味なら未対応</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>D-U10-01 / D-U10-02 ・ U2 §2.8.2</t>
     <phoneticPr fontId="2"/>
   </si>
@@ -7469,6 +7465,9 @@
   </si>
   <si>
     <t>セキュリティ設計書冒頭の「改訂待ち」注記（カード決済規格の除外・管理者のローカル認証前提）は、残タスク側の改訂2件が未実施のため残存しているもので、網羅性の穴ではない</t>
+  </si>
+  <si>
+    <t>アプリ認証方式の段階昇格を決定（第1段階=送信型の秘密情報／第2段階=鍵ペア方式へ一括昇格／第3段階=相互証明書方式は金融要件発生時のみ）。要件の意図は「アプリの身元証明」で確定（用語集と要件の配置で裏取り済み、利用者本人の証明書ログイン要件は不在）。第3段階の実施条件のみ未確定のため部分</t>
   </si>
 </sst>
 </file>
@@ -10042,48 +10041,48 @@
     </row>
     <row r="74" spans="1:5">
       <c r="A74" s="70" t="s">
-        <v>2386</v>
+        <v>2385</v>
       </c>
       <c r="B74" s="5"/>
     </row>
     <row r="75" spans="1:5" ht="85">
       <c r="A75" s="71" t="s">
+        <v>2386</v>
+      </c>
+      <c r="B75" s="73" t="s">
         <v>2387</v>
-      </c>
-      <c r="B75" s="73" t="s">
-        <v>2388</v>
       </c>
     </row>
     <row r="76" spans="1:5" ht="68">
       <c r="A76" s="71" t="s">
+        <v>2388</v>
+      </c>
+      <c r="B76" s="74" t="s">
         <v>2389</v>
-      </c>
-      <c r="B76" s="74" t="s">
-        <v>2390</v>
       </c>
     </row>
     <row r="77" spans="1:5" ht="68">
       <c r="A77" s="72" t="s">
+        <v>2390</v>
+      </c>
+      <c r="B77" s="73" t="s">
         <v>2391</v>
-      </c>
-      <c r="B77" s="73" t="s">
-        <v>2392</v>
       </c>
     </row>
     <row r="78" spans="1:5" ht="68">
       <c r="A78" s="72" t="s">
+        <v>2392</v>
+      </c>
+      <c r="B78" s="73" t="s">
         <v>2393</v>
-      </c>
-      <c r="B78" s="73" t="s">
-        <v>2394</v>
       </c>
     </row>
     <row r="79" spans="1:5" ht="85">
       <c r="A79" s="72" t="s">
+        <v>2394</v>
+      </c>
+      <c r="B79" s="75" t="s">
         <v>2395</v>
-      </c>
-      <c r="B79" s="75" t="s">
-        <v>2396</v>
       </c>
     </row>
   </sheetData>
@@ -20310,7 +20309,7 @@
         <v>1731</v>
       </c>
       <c r="H11" s="8" t="s">
-        <v>2363</v>
+        <v>2396</v>
       </c>
     </row>
     <row r="12" spans="1:8">
@@ -20691,7 +20690,7 @@
         <v>未着手</v>
       </c>
       <c r="E24" s="7" t="s">
-        <v>2364</v>
+        <v>2363</v>
       </c>
       <c r="F24" s="15" t="s">
         <v>2210</v>
@@ -20700,7 +20699,7 @@
         <v>1739</v>
       </c>
       <c r="H24" s="8" t="s">
-        <v>2365</v>
+        <v>2364</v>
       </c>
     </row>
     <row r="25" spans="1:8">
@@ -21981,16 +21980,16 @@
         <v>検討中</v>
       </c>
       <c r="E67" s="7" t="s">
+        <v>2365</v>
+      </c>
+      <c r="F67" s="15" t="s">
         <v>2366</v>
-      </c>
-      <c r="F67" s="15" t="s">
-        <v>2367</v>
       </c>
       <c r="G67" s="15" t="s">
         <v>1746</v>
       </c>
       <c r="H67" s="8" t="s">
-        <v>2368</v>
+        <v>2367</v>
       </c>
     </row>
     <row r="68" spans="1:8">
@@ -22581,7 +22580,7 @@
         <v>確定</v>
       </c>
       <c r="E87" s="7" t="s">
-        <v>2369</v>
+        <v>2368</v>
       </c>
       <c r="F87" s="15" t="s">
         <v>2203</v>
@@ -22590,7 +22589,7 @@
         <v>1739</v>
       </c>
       <c r="H87" s="8" t="s">
-        <v>2370</v>
+        <v>2369</v>
       </c>
     </row>
     <row r="88" spans="1:8">
@@ -23901,7 +23900,7 @@
         <v>未着手</v>
       </c>
       <c r="E131" s="7" t="s">
-        <v>2371</v>
+        <v>2370</v>
       </c>
       <c r="F131" s="15" t="s">
         <v>1838</v>
@@ -23910,7 +23909,7 @@
         <v>1731</v>
       </c>
       <c r="H131" s="8" t="s">
-        <v>2372</v>
+        <v>2371</v>
       </c>
     </row>
     <row r="132" spans="1:8">
@@ -24621,16 +24620,16 @@
         <v>検討中</v>
       </c>
       <c r="E155" s="7" t="s">
+        <v>2372</v>
+      </c>
+      <c r="F155" s="15" t="s">
         <v>2373</v>
-      </c>
-      <c r="F155" s="15" t="s">
-        <v>2374</v>
       </c>
       <c r="G155" s="15" t="s">
         <v>1739</v>
       </c>
       <c r="H155" s="8" t="s">
-        <v>2375</v>
+        <v>2374</v>
       </c>
     </row>
     <row r="156" spans="1:8">
@@ -24711,16 +24710,16 @@
         <v>未着手</v>
       </c>
       <c r="E158" s="7" t="s">
-        <v>2376</v>
+        <v>2375</v>
       </c>
       <c r="F158" s="15" t="s">
-        <v>2374</v>
+        <v>2373</v>
       </c>
       <c r="G158" s="15" t="s">
         <v>1746</v>
       </c>
       <c r="H158" s="8" t="s">
-        <v>2377</v>
+        <v>2376</v>
       </c>
     </row>
     <row r="159" spans="1:8">
@@ -24771,16 +24770,16 @@
         <v>未着手</v>
       </c>
       <c r="E160" s="7" t="s">
-        <v>2376</v>
+        <v>2375</v>
       </c>
       <c r="F160" s="15" t="s">
-        <v>2374</v>
+        <v>2373</v>
       </c>
       <c r="G160" s="15" t="s">
         <v>1746</v>
       </c>
       <c r="H160" s="8" t="s">
-        <v>2378</v>
+        <v>2377</v>
       </c>
     </row>
     <row r="161" spans="1:8">
@@ -24801,16 +24800,16 @@
         <v>未着手</v>
       </c>
       <c r="E161" s="7" t="s">
-        <v>2376</v>
+        <v>2375</v>
       </c>
       <c r="F161" s="15" t="s">
-        <v>2374</v>
+        <v>2373</v>
       </c>
       <c r="G161" s="15" t="s">
         <v>1746</v>
       </c>
       <c r="H161" s="8" t="s">
-        <v>2379</v>
+        <v>2378</v>
       </c>
     </row>
     <row r="162" spans="1:8">
@@ -24831,16 +24830,16 @@
         <v>未着手</v>
       </c>
       <c r="E162" s="7" t="s">
-        <v>2380</v>
+        <v>2379</v>
       </c>
       <c r="F162" s="15" t="s">
-        <v>2374</v>
+        <v>2373</v>
       </c>
       <c r="G162" s="15" t="s">
         <v>1746</v>
       </c>
       <c r="H162" s="8" t="s">
-        <v>2381</v>
+        <v>2380</v>
       </c>
     </row>
     <row r="163" spans="1:8">
@@ -25011,16 +25010,16 @@
         <v>確定</v>
       </c>
       <c r="E168" s="7" t="s">
-        <v>2382</v>
+        <v>2381</v>
       </c>
       <c r="F168" s="15" t="s">
-        <v>2374</v>
+        <v>2373</v>
       </c>
       <c r="G168" s="15" t="s">
         <v>1746</v>
       </c>
       <c r="H168" s="8" t="s">
-        <v>2383</v>
+        <v>2382</v>
       </c>
     </row>
     <row r="169" spans="1:8">
@@ -25071,16 +25070,16 @@
         <v>確定</v>
       </c>
       <c r="E170" s="7" t="s">
-        <v>2382</v>
+        <v>2381</v>
       </c>
       <c r="F170" s="15" t="s">
-        <v>2374</v>
+        <v>2373</v>
       </c>
       <c r="G170" s="15" t="s">
         <v>1746</v>
       </c>
       <c r="H170" s="8" t="s">
-        <v>2384</v>
+        <v>2383</v>
       </c>
     </row>
     <row r="171" spans="1:8">
@@ -25101,16 +25100,16 @@
         <v>検討中</v>
       </c>
       <c r="E171" s="7" t="s">
-        <v>2382</v>
+        <v>2381</v>
       </c>
       <c r="F171" s="15" t="s">
-        <v>2374</v>
+        <v>2373</v>
       </c>
       <c r="G171" s="15" t="s">
         <v>1746</v>
       </c>
       <c r="H171" s="8" t="s">
-        <v>2384</v>
+        <v>2383</v>
       </c>
     </row>
     <row r="172" spans="1:8">
@@ -25161,16 +25160,16 @@
         <v>検討中</v>
       </c>
       <c r="E173" s="7" t="s">
+        <v>2372</v>
+      </c>
+      <c r="F173" s="15" t="s">
         <v>2373</v>
-      </c>
-      <c r="F173" s="15" t="s">
-        <v>2374</v>
       </c>
       <c r="G173" s="15" t="s">
         <v>1739</v>
       </c>
       <c r="H173" s="8" t="s">
-        <v>2385</v>
+        <v>2384</v>
       </c>
     </row>
     <row r="174" spans="1:8">
@@ -25221,16 +25220,16 @@
         <v>確定</v>
       </c>
       <c r="E175" s="7" t="s">
-        <v>2382</v>
+        <v>2381</v>
       </c>
       <c r="F175" s="15" t="s">
-        <v>2374</v>
+        <v>2373</v>
       </c>
       <c r="G175" s="15" t="s">
         <v>1746</v>
       </c>
       <c r="H175" s="8" t="s">
-        <v>2384</v>
+        <v>2383</v>
       </c>
     </row>
     <row r="176" spans="1:8">
@@ -25251,16 +25250,16 @@
         <v>確定</v>
       </c>
       <c r="E176" s="7" t="s">
-        <v>2382</v>
+        <v>2381</v>
       </c>
       <c r="F176" s="15" t="s">
-        <v>2374</v>
+        <v>2373</v>
       </c>
       <c r="G176" s="15" t="s">
         <v>1746</v>
       </c>
       <c r="H176" s="8" t="s">
-        <v>2384</v>
+        <v>2383</v>
       </c>
     </row>
     <row r="177" spans="1:8">

--- a/doc/excel/認証タスク.xlsx
+++ b/doc/excel/認証タスク.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/suepie/Develop/10_project/aws-atuh-poc/doc/excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D510BD1-98A6-D446-9369-55291F398F75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07123452-2542-1747-87F9-FB3D1B10C85E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="780" windowWidth="34200" windowHeight="21460" activeTab="7" xr2:uid="{B021B529-7D79-6D49-8055-5FE1DF3A55F9}"/>
   </bookViews>

--- a/doc/excel/認証タスク.xlsx
+++ b/doc/excel/認証タスク.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/suepie/Develop/10_project/aws-atuh-poc/doc/excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6DAB9C51-B8FD-F04F-94C1-B3DDEE12C295}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F110089A-714F-204F-8AD3-7AB8A5939002}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="780" windowWidth="34200" windowHeight="21460" firstSheet="1" activeTab="4" xr2:uid="{B021B529-7D79-6D49-8055-5FE1DF3A55F9}"/>
   </bookViews>

--- a/doc/excel/認証タスク.xlsx
+++ b/doc/excel/認証タスク.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/suepie/Develop/10_project/aws-atuh-poc/doc/excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{736757D9-8E35-894F-AB26-1E18679C3B37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85085E80-7D94-2B45-BB4A-EF6750CF2949}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="780" windowWidth="34200" windowHeight="21460" xr2:uid="{B021B529-7D79-6D49-8055-5FE1DF3A55F9}"/>
+    <workbookView xWindow="0" yWindow="780" windowWidth="34200" windowHeight="21460" firstSheet="7" activeTab="16" xr2:uid="{B021B529-7D79-6D49-8055-5FE1DF3A55F9}"/>
   </bookViews>
   <sheets>
     <sheet name="調査依頼プロンプト（一時）" sheetId="11" r:id="rId1"/>

--- a/doc/excel/認証タスク.xlsx
+++ b/doc/excel/認証タスク.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/suepie/Develop/10_project/aws-atuh-poc/doc/excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85085E80-7D94-2B45-BB4A-EF6750CF2949}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7AA9B5C7-0418-3740-B04D-880D549C09D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="780" windowWidth="34200" windowHeight="21460" firstSheet="7" activeTab="16" xr2:uid="{B021B529-7D79-6D49-8055-5FE1DF3A55F9}"/>
+    <workbookView xWindow="-2480" yWindow="-21600" windowWidth="38400" windowHeight="21600" firstSheet="2" activeTab="11" xr2:uid="{B021B529-7D79-6D49-8055-5FE1DF3A55F9}"/>
   </bookViews>
   <sheets>
     <sheet name="調査依頼プロンプト（一時）" sheetId="11" r:id="rId1"/>

--- a/doc/excel/認証タスク.xlsx
+++ b/doc/excel/認証タスク.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/suepie/Develop/10_project/aws-atuh-poc/doc/excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7AA9B5C7-0418-3740-B04D-880D549C09D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF87D5E5-B88A-794E-9645-318B0CA6E303}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-2480" yWindow="-21600" windowWidth="38400" windowHeight="21600" firstSheet="2" activeTab="11" xr2:uid="{B021B529-7D79-6D49-8055-5FE1DF3A55F9}"/>
+    <workbookView xWindow="-2480" yWindow="-21600" windowWidth="38400" windowHeight="21600" firstSheet="5" activeTab="16" xr2:uid="{B021B529-7D79-6D49-8055-5FE1DF3A55F9}"/>
   </bookViews>
   <sheets>
     <sheet name="調査依頼プロンプト（一時）" sheetId="11" r:id="rId1"/>

--- a/doc/excel/認証タスク.xlsx
+++ b/doc/excel/認証タスク.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/suepie/Develop/10_project/aws-atuh-poc/doc/excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41CDBCAB-E03B-F140-9FA5-3FAFF74D9875}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36EF1175-127E-CA47-8DE7-1297E812DA0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="38400" windowHeight="21600" activeTab="4" xr2:uid="{B021B529-7D79-6D49-8055-5FE1DF3A55F9}"/>
+    <workbookView xWindow="0" yWindow="780" windowWidth="34200" windowHeight="21460" activeTab="4" xr2:uid="{B021B529-7D79-6D49-8055-5FE1DF3A55F9}"/>
   </bookViews>
   <sheets>
     <sheet name="コスト見積もり" sheetId="12" r:id="rId1"/>

--- a/doc/excel/認証タスク.xlsx
+++ b/doc/excel/認証タスク.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/suepie/Develop/10_project/aws-atuh-poc/doc/excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90B25343-467F-F64D-827B-91C217D648A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5F4C251-A8E4-5B4D-A99B-808B53FE9C46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="780" windowWidth="34200" windowHeight="21460" activeTab="5" xr2:uid="{B021B529-7D79-6D49-8055-5FE1DF3A55F9}"/>
   </bookViews>

--- a/doc/excel/認証タスク.xlsx
+++ b/doc/excel/認証タスク.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/suepie/Develop/10_project/aws-atuh-poc/doc/excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54BDFDBF-A05D-5D47-A40E-C0B76D859225}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47580328-AC4A-824A-907C-A45A7D544D99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="780" windowWidth="34200" windowHeight="21460" firstSheet="2" activeTab="10" xr2:uid="{B021B529-7D79-6D49-8055-5FE1DF3A55F9}"/>
   </bookViews>

--- a/doc/excel/認証タスク.xlsx
+++ b/doc/excel/認証タスク.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/suepie/Develop/10_project/aws-atuh-poc/doc/excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47580328-AC4A-824A-907C-A45A7D544D99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4218343-AFDB-EA40-81AE-3750E6A1FA8B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="780" windowWidth="34200" windowHeight="21460" firstSheet="2" activeTab="10" xr2:uid="{B021B529-7D79-6D49-8055-5FE1DF3A55F9}"/>
   </bookViews>
@@ -56,7 +56,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8750" uniqueCount="4109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8750" uniqueCount="4110">
   <si>
     <t>区分</t>
   </si>
@@ -13120,6 +13120,10 @@
     <rPh sb="0" eb="2">
       <t>ガイブ</t>
     </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>HB-F-AZ-07</t>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -19293,11 +19297,11 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20"/>
   <cols>
     <col min="1" max="1" width="15.7109375" customWidth="1"/>
-    <col min="2" max="2" width="35.7109375" customWidth="1"/>
-    <col min="3" max="3" width="11.42578125" customWidth="1"/>
-    <col min="4" max="4" width="47.140625" customWidth="1"/>
-    <col min="5" max="5" width="15.7109375" customWidth="1"/>
-    <col min="6" max="9" width="7.140625" customWidth="1"/>
+    <col min="2" max="2" width="11.42578125" customWidth="1"/>
+    <col min="3" max="3" width="15.7109375" customWidth="1"/>
+    <col min="4" max="4" width="46.140625" customWidth="1"/>
+    <col min="5" max="5" width="70.42578125" customWidth="1"/>
+    <col min="6" max="9" width="9.28515625" customWidth="1"/>
     <col min="10" max="10" width="32.85546875" customWidth="1"/>
   </cols>
   <sheetData>
@@ -19306,16 +19310,16 @@
         <v>285</v>
       </c>
       <c r="B1" s="163" t="s">
+        <v>330</v>
+      </c>
+      <c r="C1" s="163" t="s">
+        <v>3657</v>
+      </c>
+      <c r="D1" s="163" t="s">
         <v>1232</v>
       </c>
-      <c r="C1" s="163" t="s">
-        <v>330</v>
-      </c>
-      <c r="D1" s="163" t="s">
+      <c r="E1" s="163" t="s">
         <v>5</v>
-      </c>
-      <c r="E1" s="163" t="s">
-        <v>3657</v>
       </c>
       <c r="F1" s="163" t="s">
         <v>2037</v>
@@ -19338,16 +19342,16 @@
         <v>7</v>
       </c>
       <c r="B2" s="102" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" s="102" t="s">
+        <v>3660</v>
+      </c>
+      <c r="D2" s="102" t="s">
         <v>3658</v>
       </c>
-      <c r="C2" s="102" t="s">
-        <v>2</v>
-      </c>
-      <c r="D2" s="102" t="s">
+      <c r="E2" s="102" t="s">
         <v>3659</v>
-      </c>
-      <c r="E2" s="102" t="s">
-        <v>3660</v>
       </c>
       <c r="F2" s="102" t="s">
         <v>3922</v>
@@ -19370,16 +19374,16 @@
         <v>8</v>
       </c>
       <c r="B3" s="102" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3" s="102" t="s">
+        <v>3663</v>
+      </c>
+      <c r="D3" s="102" t="s">
         <v>3661</v>
       </c>
-      <c r="C3" s="102" t="s">
-        <v>2</v>
-      </c>
-      <c r="D3" s="102" t="s">
+      <c r="E3" s="102" t="s">
         <v>3662</v>
-      </c>
-      <c r="E3" s="102" t="s">
-        <v>3663</v>
       </c>
       <c r="F3" s="102" t="s">
         <v>3925</v>
@@ -19402,16 +19406,16 @@
         <v>9</v>
       </c>
       <c r="B4" s="102" t="s">
+        <v>2</v>
+      </c>
+      <c r="C4" s="102" t="s">
+        <v>3663</v>
+      </c>
+      <c r="D4" s="102" t="s">
         <v>10</v>
       </c>
-      <c r="C4" s="102" t="s">
-        <v>2</v>
-      </c>
-      <c r="D4" s="102" t="s">
+      <c r="E4" s="102" t="s">
         <v>3664</v>
-      </c>
-      <c r="E4" s="102" t="s">
-        <v>3663</v>
       </c>
       <c r="F4" s="102" t="s">
         <v>3925</v>
@@ -19434,19 +19438,19 @@
         <v>11</v>
       </c>
       <c r="B5" s="102" t="s">
+        <v>2</v>
+      </c>
+      <c r="C5" s="102" t="s">
+        <v>3663</v>
+      </c>
+      <c r="D5" s="102" t="s">
         <v>12</v>
       </c>
-      <c r="C5" s="102" t="s">
-        <v>2</v>
-      </c>
-      <c r="D5" s="102" t="s">
+      <c r="E5" s="102" t="s">
         <v>3665</v>
       </c>
-      <c r="E5" s="102" t="s">
-        <v>3663</v>
-      </c>
       <c r="F5" s="102" t="s">
-        <v>1767</v>
+        <v>4109</v>
       </c>
       <c r="G5" s="102" t="s">
         <v>2024</v>
@@ -19466,16 +19470,16 @@
         <v>13</v>
       </c>
       <c r="B6" s="102" t="s">
+        <v>2</v>
+      </c>
+      <c r="C6" s="102" t="s">
+        <v>286</v>
+      </c>
+      <c r="D6" s="102" t="s">
         <v>14</v>
       </c>
-      <c r="C6" s="102" t="s">
-        <v>2</v>
-      </c>
-      <c r="D6" s="102" t="s">
+      <c r="E6" s="102" t="s">
         <v>3666</v>
-      </c>
-      <c r="E6" s="102" t="s">
-        <v>286</v>
       </c>
       <c r="F6" s="102"/>
       <c r="G6" s="102"/>
@@ -19490,16 +19494,16 @@
         <v>15</v>
       </c>
       <c r="B7" s="102" t="s">
+        <v>2</v>
+      </c>
+      <c r="C7" s="102" t="s">
+        <v>286</v>
+      </c>
+      <c r="D7" s="102" t="s">
         <v>3667</v>
       </c>
-      <c r="C7" s="102" t="s">
-        <v>2</v>
-      </c>
-      <c r="D7" s="102" t="s">
+      <c r="E7" s="102" t="s">
         <v>3668</v>
-      </c>
-      <c r="E7" s="102" t="s">
-        <v>286</v>
       </c>
       <c r="F7" s="102"/>
       <c r="G7" s="102"/>
@@ -19514,16 +19518,16 @@
         <v>16</v>
       </c>
       <c r="B8" s="102" t="s">
+        <v>2</v>
+      </c>
+      <c r="C8" s="102" t="s">
+        <v>286</v>
+      </c>
+      <c r="D8" s="102" t="s">
         <v>3669</v>
       </c>
-      <c r="C8" s="102" t="s">
-        <v>2</v>
-      </c>
-      <c r="D8" s="102" t="s">
+      <c r="E8" s="102" t="s">
         <v>3670</v>
-      </c>
-      <c r="E8" s="102" t="s">
-        <v>286</v>
       </c>
       <c r="F8" s="102"/>
       <c r="G8" s="102"/>
@@ -19538,16 +19542,16 @@
         <v>17</v>
       </c>
       <c r="B9" s="102" t="s">
+        <v>2</v>
+      </c>
+      <c r="C9" s="102" t="s">
+        <v>286</v>
+      </c>
+      <c r="D9" s="102" t="s">
         <v>18</v>
       </c>
-      <c r="C9" s="102" t="s">
-        <v>2</v>
-      </c>
-      <c r="D9" s="102" t="s">
+      <c r="E9" s="102" t="s">
         <v>3671</v>
-      </c>
-      <c r="E9" s="102" t="s">
-        <v>286</v>
       </c>
       <c r="F9" s="102"/>
       <c r="G9" s="102"/>
@@ -19562,16 +19566,16 @@
         <v>19</v>
       </c>
       <c r="B10" s="102" t="s">
+        <v>2</v>
+      </c>
+      <c r="C10" s="102" t="s">
+        <v>3660</v>
+      </c>
+      <c r="D10" s="102" t="s">
         <v>20</v>
       </c>
-      <c r="C10" s="102" t="s">
-        <v>2</v>
-      </c>
-      <c r="D10" s="102" t="s">
+      <c r="E10" s="102" t="s">
         <v>3672</v>
-      </c>
-      <c r="E10" s="102" t="s">
-        <v>3660</v>
       </c>
       <c r="F10" s="102" t="s">
         <v>3922</v>
@@ -19594,16 +19598,16 @@
         <v>21</v>
       </c>
       <c r="B11" s="102" t="s">
+        <v>2</v>
+      </c>
+      <c r="C11" s="102" t="s">
+        <v>3660</v>
+      </c>
+      <c r="D11" s="102" t="s">
         <v>3673</v>
       </c>
-      <c r="C11" s="102" t="s">
-        <v>2</v>
-      </c>
-      <c r="D11" s="102" t="s">
+      <c r="E11" s="102" t="s">
         <v>3674</v>
-      </c>
-      <c r="E11" s="102" t="s">
-        <v>3660</v>
       </c>
       <c r="F11" s="102" t="s">
         <v>3922</v>
@@ -19626,16 +19630,16 @@
         <v>22</v>
       </c>
       <c r="B12" s="102" t="s">
+        <v>2</v>
+      </c>
+      <c r="C12" s="102" t="s">
+        <v>3660</v>
+      </c>
+      <c r="D12" s="102" t="s">
         <v>3675</v>
       </c>
-      <c r="C12" s="102" t="s">
-        <v>2</v>
-      </c>
-      <c r="D12" s="102" t="s">
+      <c r="E12" s="102" t="s">
         <v>3676</v>
-      </c>
-      <c r="E12" s="102" t="s">
-        <v>3660</v>
       </c>
       <c r="F12" s="102" t="s">
         <v>1755</v>
@@ -19658,16 +19662,16 @@
         <v>23</v>
       </c>
       <c r="B13" s="102" t="s">
+        <v>2</v>
+      </c>
+      <c r="C13" s="102" t="s">
+        <v>3660</v>
+      </c>
+      <c r="D13" s="102" t="s">
         <v>24</v>
       </c>
-      <c r="C13" s="102" t="s">
-        <v>2</v>
-      </c>
-      <c r="D13" s="102" t="s">
+      <c r="E13" s="102" t="s">
         <v>3677</v>
-      </c>
-      <c r="E13" s="102" t="s">
-        <v>3660</v>
       </c>
       <c r="F13" s="102" t="s">
         <v>3922</v>
@@ -19690,16 +19694,16 @@
         <v>25</v>
       </c>
       <c r="B14" s="102" t="s">
+        <v>2</v>
+      </c>
+      <c r="C14" s="102" t="s">
+        <v>3660</v>
+      </c>
+      <c r="D14" s="102" t="s">
         <v>3678</v>
       </c>
-      <c r="C14" s="102" t="s">
-        <v>2</v>
-      </c>
-      <c r="D14" s="102" t="s">
+      <c r="E14" s="102" t="s">
         <v>3679</v>
-      </c>
-      <c r="E14" s="102" t="s">
-        <v>3660</v>
       </c>
       <c r="F14" s="102"/>
       <c r="G14" s="102"/>
@@ -19714,16 +19718,16 @@
         <v>26</v>
       </c>
       <c r="B15" s="102" t="s">
+        <v>2</v>
+      </c>
+      <c r="C15" s="102" t="s">
+        <v>3660</v>
+      </c>
+      <c r="D15" s="102" t="s">
         <v>27</v>
       </c>
-      <c r="C15" s="102" t="s">
-        <v>2</v>
-      </c>
-      <c r="D15" s="102" t="s">
+      <c r="E15" s="102" t="s">
         <v>3680</v>
-      </c>
-      <c r="E15" s="102" t="s">
-        <v>3660</v>
       </c>
       <c r="F15" s="102"/>
       <c r="G15" s="102"/>
@@ -19738,16 +19742,16 @@
         <v>3681</v>
       </c>
       <c r="B16" s="102" t="s">
+        <v>2</v>
+      </c>
+      <c r="C16" s="102" t="s">
+        <v>286</v>
+      </c>
+      <c r="D16" s="102" t="s">
         <v>3682</v>
       </c>
-      <c r="C16" s="102" t="s">
-        <v>2</v>
-      </c>
-      <c r="D16" s="102" t="s">
+      <c r="E16" s="102" t="s">
         <v>3683</v>
-      </c>
-      <c r="E16" s="102" t="s">
-        <v>286</v>
       </c>
       <c r="F16" s="102"/>
       <c r="G16" s="102"/>
@@ -19762,16 +19766,16 @@
         <v>28</v>
       </c>
       <c r="B17" s="102" t="s">
+        <v>2</v>
+      </c>
+      <c r="C17" s="102" t="s">
+        <v>3663</v>
+      </c>
+      <c r="D17" s="102" t="s">
         <v>3684</v>
       </c>
-      <c r="C17" s="102" t="s">
-        <v>2</v>
-      </c>
-      <c r="D17" s="102" t="s">
+      <c r="E17" s="102" t="s">
         <v>3685</v>
-      </c>
-      <c r="E17" s="102" t="s">
-        <v>3663</v>
       </c>
       <c r="F17" s="102" t="s">
         <v>3933</v>
@@ -19794,16 +19798,16 @@
         <v>29</v>
       </c>
       <c r="B18" s="102" t="s">
+        <v>2</v>
+      </c>
+      <c r="C18" s="102" t="s">
+        <v>3663</v>
+      </c>
+      <c r="D18" s="102" t="s">
         <v>3686</v>
       </c>
-      <c r="C18" s="102" t="s">
-        <v>2</v>
-      </c>
-      <c r="D18" s="102" t="s">
+      <c r="E18" s="102" t="s">
         <v>3687</v>
-      </c>
-      <c r="E18" s="102" t="s">
-        <v>3663</v>
       </c>
       <c r="F18" s="102" t="s">
         <v>3933</v>
@@ -19826,16 +19830,16 @@
         <v>30</v>
       </c>
       <c r="B19" s="102" t="s">
+        <v>2</v>
+      </c>
+      <c r="C19" s="102" t="s">
+        <v>3663</v>
+      </c>
+      <c r="D19" s="102" t="s">
         <v>3688</v>
       </c>
-      <c r="C19" s="102" t="s">
-        <v>2</v>
-      </c>
-      <c r="D19" s="102" t="s">
+      <c r="E19" s="102" t="s">
         <v>3689</v>
-      </c>
-      <c r="E19" s="102" t="s">
-        <v>3663</v>
       </c>
       <c r="F19" s="102" t="s">
         <v>3933</v>
@@ -19858,16 +19862,16 @@
         <v>31</v>
       </c>
       <c r="B20" s="102" t="s">
+        <v>2</v>
+      </c>
+      <c r="C20" s="102" t="s">
+        <v>3663</v>
+      </c>
+      <c r="D20" s="102" t="s">
         <v>3690</v>
       </c>
-      <c r="C20" s="102" t="s">
-        <v>2</v>
-      </c>
-      <c r="D20" s="102" t="s">
+      <c r="E20" s="102" t="s">
         <v>3691</v>
-      </c>
-      <c r="E20" s="102" t="s">
-        <v>3663</v>
       </c>
       <c r="F20" s="102" t="s">
         <v>3933</v>
@@ -19890,16 +19894,16 @@
         <v>32</v>
       </c>
       <c r="B21" s="102" t="s">
+        <v>2</v>
+      </c>
+      <c r="C21" s="102" t="s">
+        <v>3663</v>
+      </c>
+      <c r="D21" s="102" t="s">
         <v>3692</v>
       </c>
-      <c r="C21" s="102" t="s">
-        <v>2</v>
-      </c>
-      <c r="D21" s="102" t="s">
+      <c r="E21" s="102" t="s">
         <v>3693</v>
-      </c>
-      <c r="E21" s="102" t="s">
-        <v>3663</v>
       </c>
       <c r="F21" s="102" t="s">
         <v>3938</v>
@@ -19922,16 +19926,16 @@
         <v>33</v>
       </c>
       <c r="B22" s="102" t="s">
+        <v>2</v>
+      </c>
+      <c r="C22" s="102" t="s">
+        <v>3663</v>
+      </c>
+      <c r="D22" s="102" t="s">
         <v>3694</v>
       </c>
-      <c r="C22" s="102" t="s">
-        <v>2</v>
-      </c>
-      <c r="D22" s="102" t="s">
+      <c r="E22" s="102" t="s">
         <v>3695</v>
-      </c>
-      <c r="E22" s="102" t="s">
-        <v>3663</v>
       </c>
       <c r="F22" s="102" t="s">
         <v>3942</v>
@@ -19954,16 +19958,16 @@
         <v>34</v>
       </c>
       <c r="B23" s="102" t="s">
+        <v>2</v>
+      </c>
+      <c r="C23" s="102" t="s">
+        <v>286</v>
+      </c>
+      <c r="D23" s="102" t="s">
         <v>35</v>
       </c>
-      <c r="C23" s="102" t="s">
-        <v>2</v>
-      </c>
-      <c r="D23" s="102" t="s">
+      <c r="E23" s="102" t="s">
         <v>3696</v>
-      </c>
-      <c r="E23" s="102" t="s">
-        <v>286</v>
       </c>
       <c r="F23" s="102"/>
       <c r="G23" s="102"/>
@@ -19978,16 +19982,16 @@
         <v>37</v>
       </c>
       <c r="B24" s="102" t="s">
+        <v>2</v>
+      </c>
+      <c r="C24" s="102" t="s">
+        <v>3663</v>
+      </c>
+      <c r="D24" s="102" t="s">
         <v>3697</v>
       </c>
-      <c r="C24" s="102" t="s">
-        <v>2</v>
-      </c>
-      <c r="D24" s="102" t="s">
+      <c r="E24" s="102" t="s">
         <v>3698</v>
-      </c>
-      <c r="E24" s="102" t="s">
-        <v>3663</v>
       </c>
       <c r="F24" s="102" t="s">
         <v>1750</v>
@@ -20010,16 +20014,16 @@
         <v>38</v>
       </c>
       <c r="B25" s="102" t="s">
+        <v>2</v>
+      </c>
+      <c r="C25" s="102" t="s">
+        <v>3663</v>
+      </c>
+      <c r="D25" s="102" t="s">
         <v>3699</v>
       </c>
-      <c r="C25" s="102" t="s">
-        <v>2</v>
-      </c>
-      <c r="D25" s="102" t="s">
+      <c r="E25" s="102" t="s">
         <v>3700</v>
-      </c>
-      <c r="E25" s="102" t="s">
-        <v>3663</v>
       </c>
       <c r="F25" s="102" t="s">
         <v>3949</v>
@@ -20042,16 +20046,16 @@
         <v>40</v>
       </c>
       <c r="B26" s="102" t="s">
+        <v>2</v>
+      </c>
+      <c r="C26" s="102" t="s">
+        <v>3663</v>
+      </c>
+      <c r="D26" s="102" t="s">
         <v>3701</v>
       </c>
-      <c r="C26" s="102" t="s">
-        <v>2</v>
-      </c>
-      <c r="D26" s="102" t="s">
+      <c r="E26" s="102" t="s">
         <v>3702</v>
-      </c>
-      <c r="E26" s="102" t="s">
-        <v>3663</v>
       </c>
       <c r="F26" s="102" t="s">
         <v>3953</v>
@@ -20074,16 +20078,16 @@
         <v>41</v>
       </c>
       <c r="B27" s="102" t="s">
+        <v>2</v>
+      </c>
+      <c r="C27" s="102" t="s">
+        <v>3663</v>
+      </c>
+      <c r="D27" s="102" t="s">
         <v>42</v>
       </c>
-      <c r="C27" s="102" t="s">
-        <v>2</v>
-      </c>
-      <c r="D27" s="102" t="s">
+      <c r="E27" s="102" t="s">
         <v>3703</v>
-      </c>
-      <c r="E27" s="102" t="s">
-        <v>3663</v>
       </c>
       <c r="F27" s="102" t="s">
         <v>3957</v>
@@ -20106,16 +20110,16 @@
         <v>39</v>
       </c>
       <c r="B28" s="102" t="s">
+        <v>2</v>
+      </c>
+      <c r="C28" s="102" t="s">
+        <v>3706</v>
+      </c>
+      <c r="D28" s="102" t="s">
         <v>3704</v>
       </c>
-      <c r="C28" s="102" t="s">
-        <v>2</v>
-      </c>
-      <c r="D28" s="102" t="s">
+      <c r="E28" s="102" t="s">
         <v>3705</v>
-      </c>
-      <c r="E28" s="102" t="s">
-        <v>3706</v>
       </c>
       <c r="F28" s="102"/>
       <c r="G28" s="102"/>
@@ -20132,16 +20136,16 @@
         <v>43</v>
       </c>
       <c r="B29" s="102" t="s">
+        <v>2</v>
+      </c>
+      <c r="C29" s="102" t="s">
+        <v>3663</v>
+      </c>
+      <c r="D29" s="102" t="s">
         <v>3707</v>
       </c>
-      <c r="C29" s="102" t="s">
-        <v>2</v>
-      </c>
-      <c r="D29" s="102" t="s">
+      <c r="E29" s="102" t="s">
         <v>3708</v>
-      </c>
-      <c r="E29" s="102" t="s">
-        <v>3663</v>
       </c>
       <c r="F29" s="102" t="s">
         <v>3961</v>
@@ -20164,16 +20168,16 @@
         <v>36</v>
       </c>
       <c r="B30" s="102" t="s">
+        <v>2</v>
+      </c>
+      <c r="C30" s="102" t="s">
+        <v>286</v>
+      </c>
+      <c r="D30" s="102" t="s">
         <v>3709</v>
       </c>
-      <c r="C30" s="102" t="s">
-        <v>2</v>
-      </c>
-      <c r="D30" s="102" t="s">
+      <c r="E30" s="102" t="s">
         <v>3710</v>
-      </c>
-      <c r="E30" s="102" t="s">
-        <v>286</v>
       </c>
       <c r="F30" s="102"/>
       <c r="G30" s="102"/>
@@ -20188,16 +20192,16 @@
         <v>44</v>
       </c>
       <c r="B31" s="102" t="s">
+        <v>2</v>
+      </c>
+      <c r="C31" s="102" t="s">
+        <v>3660</v>
+      </c>
+      <c r="D31" s="102" t="s">
         <v>3711</v>
       </c>
-      <c r="C31" s="102" t="s">
-        <v>2</v>
-      </c>
-      <c r="D31" s="102" t="s">
+      <c r="E31" s="102" t="s">
         <v>3712</v>
-      </c>
-      <c r="E31" s="102" t="s">
-        <v>3660</v>
       </c>
       <c r="F31" s="102"/>
       <c r="G31" s="102"/>
@@ -20212,16 +20216,16 @@
         <v>45</v>
       </c>
       <c r="B32" s="102" t="s">
+        <v>2</v>
+      </c>
+      <c r="C32" s="102" t="s">
+        <v>3660</v>
+      </c>
+      <c r="D32" s="102" t="s">
         <v>46</v>
       </c>
-      <c r="C32" s="102" t="s">
-        <v>2</v>
-      </c>
-      <c r="D32" s="102" t="s">
+      <c r="E32" s="102" t="s">
         <v>3713</v>
-      </c>
-      <c r="E32" s="102" t="s">
-        <v>3660</v>
       </c>
       <c r="F32" s="102"/>
       <c r="G32" s="102"/>
@@ -20236,16 +20240,16 @@
         <v>47</v>
       </c>
       <c r="B33" s="102" t="s">
+        <v>2</v>
+      </c>
+      <c r="C33" s="102" t="s">
+        <v>286</v>
+      </c>
+      <c r="D33" s="102" t="s">
         <v>48</v>
       </c>
-      <c r="C33" s="102" t="s">
-        <v>2</v>
-      </c>
-      <c r="D33" s="102" t="s">
+      <c r="E33" s="102" t="s">
         <v>3714</v>
-      </c>
-      <c r="E33" s="102" t="s">
-        <v>286</v>
       </c>
       <c r="F33" s="102"/>
       <c r="G33" s="102"/>
@@ -20260,16 +20264,16 @@
         <v>49</v>
       </c>
       <c r="B34" s="102" t="s">
+        <v>2</v>
+      </c>
+      <c r="C34" s="102" t="s">
+        <v>286</v>
+      </c>
+      <c r="D34" s="102" t="s">
         <v>3715</v>
       </c>
-      <c r="C34" s="102" t="s">
-        <v>2</v>
-      </c>
-      <c r="D34" s="102" t="s">
+      <c r="E34" s="102" t="s">
         <v>3716</v>
-      </c>
-      <c r="E34" s="102" t="s">
-        <v>286</v>
       </c>
       <c r="F34" s="102"/>
       <c r="G34" s="102"/>
@@ -20284,16 +20288,16 @@
         <v>50</v>
       </c>
       <c r="B35" s="102" t="s">
+        <v>2</v>
+      </c>
+      <c r="C35" s="102" t="s">
+        <v>3660</v>
+      </c>
+      <c r="D35" s="102" t="s">
         <v>3717</v>
       </c>
-      <c r="C35" s="102" t="s">
-        <v>2</v>
-      </c>
-      <c r="D35" s="102" t="s">
+      <c r="E35" s="102" t="s">
         <v>3718</v>
-      </c>
-      <c r="E35" s="102" t="s">
-        <v>3660</v>
       </c>
       <c r="F35" s="102"/>
       <c r="G35" s="102"/>
@@ -20308,16 +20312,16 @@
         <v>51</v>
       </c>
       <c r="B36" s="102" t="s">
+        <v>2</v>
+      </c>
+      <c r="C36" s="102" t="s">
+        <v>286</v>
+      </c>
+      <c r="D36" s="102" t="s">
         <v>3719</v>
       </c>
-      <c r="C36" s="102" t="s">
-        <v>2</v>
-      </c>
-      <c r="D36" s="102" t="s">
+      <c r="E36" s="102" t="s">
         <v>3720</v>
-      </c>
-      <c r="E36" s="102" t="s">
-        <v>286</v>
       </c>
       <c r="F36" s="102"/>
       <c r="G36" s="102"/>
@@ -20332,16 +20336,16 @@
         <v>52</v>
       </c>
       <c r="B37" s="102" t="s">
+        <v>2</v>
+      </c>
+      <c r="C37" s="102" t="s">
+        <v>3660</v>
+      </c>
+      <c r="D37" s="102" t="s">
         <v>3721</v>
       </c>
-      <c r="C37" s="102" t="s">
-        <v>2</v>
-      </c>
-      <c r="D37" s="102" t="s">
+      <c r="E37" s="102" t="s">
         <v>3722</v>
-      </c>
-      <c r="E37" s="102" t="s">
-        <v>3660</v>
       </c>
       <c r="F37" s="102"/>
       <c r="G37" s="102"/>
@@ -20356,16 +20360,16 @@
         <v>53</v>
       </c>
       <c r="B38" s="102" t="s">
+        <v>2</v>
+      </c>
+      <c r="C38" s="102" t="s">
+        <v>286</v>
+      </c>
+      <c r="D38" s="102" t="s">
         <v>3723</v>
       </c>
-      <c r="C38" s="102" t="s">
-        <v>2</v>
-      </c>
-      <c r="D38" s="102" t="s">
+      <c r="E38" s="102" t="s">
         <v>3724</v>
-      </c>
-      <c r="E38" s="102" t="s">
-        <v>286</v>
       </c>
       <c r="F38" s="102"/>
       <c r="G38" s="102"/>
@@ -20380,16 +20384,16 @@
         <v>54</v>
       </c>
       <c r="B39" s="102" t="s">
+        <v>2</v>
+      </c>
+      <c r="C39" s="102" t="s">
+        <v>3660</v>
+      </c>
+      <c r="D39" s="102" t="s">
         <v>3725</v>
       </c>
-      <c r="C39" s="102" t="s">
-        <v>2</v>
-      </c>
-      <c r="D39" s="102" t="s">
+      <c r="E39" s="102" t="s">
         <v>3726</v>
-      </c>
-      <c r="E39" s="102" t="s">
-        <v>3660</v>
       </c>
       <c r="F39" s="102"/>
       <c r="G39" s="102"/>
@@ -20404,16 +20408,16 @@
         <v>55</v>
       </c>
       <c r="B40" s="102" t="s">
+        <v>2</v>
+      </c>
+      <c r="C40" s="102" t="s">
+        <v>3663</v>
+      </c>
+      <c r="D40" s="102" t="s">
         <v>3727</v>
       </c>
-      <c r="C40" s="102" t="s">
-        <v>2</v>
-      </c>
-      <c r="D40" s="102" t="s">
+      <c r="E40" s="102" t="s">
         <v>3728</v>
-      </c>
-      <c r="E40" s="102" t="s">
-        <v>3663</v>
       </c>
       <c r="F40" s="102" t="s">
         <v>3965</v>
@@ -20436,16 +20440,16 @@
         <v>56</v>
       </c>
       <c r="B41" s="102" t="s">
+        <v>2</v>
+      </c>
+      <c r="C41" s="102" t="s">
+        <v>3663</v>
+      </c>
+      <c r="D41" s="102" t="s">
         <v>3729</v>
       </c>
-      <c r="C41" s="102" t="s">
-        <v>2</v>
-      </c>
-      <c r="D41" s="102" t="s">
+      <c r="E41" s="102" t="s">
         <v>3730</v>
-      </c>
-      <c r="E41" s="102" t="s">
-        <v>3663</v>
       </c>
       <c r="F41" s="102" t="s">
         <v>3968</v>
@@ -20468,16 +20472,16 @@
         <v>57</v>
       </c>
       <c r="B42" s="102" t="s">
+        <v>2</v>
+      </c>
+      <c r="C42" s="102" t="s">
+        <v>2174</v>
+      </c>
+      <c r="D42" s="102" t="s">
         <v>3731</v>
       </c>
-      <c r="C42" s="102" t="s">
-        <v>2</v>
-      </c>
-      <c r="D42" s="102" t="s">
+      <c r="E42" s="102" t="s">
         <v>3732</v>
-      </c>
-      <c r="E42" s="102" t="s">
-        <v>2174</v>
       </c>
       <c r="F42" s="102" t="s">
         <v>1566</v>
@@ -20500,16 +20504,16 @@
         <v>58</v>
       </c>
       <c r="B43" s="102" t="s">
+        <v>2</v>
+      </c>
+      <c r="C43" s="102" t="s">
+        <v>3663</v>
+      </c>
+      <c r="D43" s="102" t="s">
         <v>3733</v>
       </c>
-      <c r="C43" s="102" t="s">
-        <v>2</v>
-      </c>
-      <c r="D43" s="102" t="s">
+      <c r="E43" s="102" t="s">
         <v>3734</v>
-      </c>
-      <c r="E43" s="102" t="s">
-        <v>3663</v>
       </c>
       <c r="F43" s="102" t="s">
         <v>3973</v>
@@ -20532,16 +20536,16 @@
         <v>59</v>
       </c>
       <c r="B44" s="102" t="s">
+        <v>2</v>
+      </c>
+      <c r="C44" s="102" t="s">
+        <v>3663</v>
+      </c>
+      <c r="D44" s="102" t="s">
         <v>3735</v>
       </c>
-      <c r="C44" s="102" t="s">
-        <v>2</v>
-      </c>
-      <c r="D44" s="102" t="s">
+      <c r="E44" s="102" t="s">
         <v>3736</v>
-      </c>
-      <c r="E44" s="102" t="s">
-        <v>3663</v>
       </c>
       <c r="F44" s="102" t="s">
         <v>3973</v>
@@ -20564,16 +20568,16 @@
         <v>60</v>
       </c>
       <c r="B45" s="102" t="s">
+        <v>2</v>
+      </c>
+      <c r="C45" s="102" t="s">
+        <v>286</v>
+      </c>
+      <c r="D45" s="102" t="s">
         <v>61</v>
       </c>
-      <c r="C45" s="102" t="s">
-        <v>2</v>
-      </c>
-      <c r="D45" s="102" t="s">
+      <c r="E45" s="102" t="s">
         <v>3737</v>
-      </c>
-      <c r="E45" s="102" t="s">
-        <v>286</v>
       </c>
       <c r="F45" s="102"/>
       <c r="G45" s="102"/>
@@ -20588,16 +20592,16 @@
         <v>62</v>
       </c>
       <c r="B46" s="102" t="s">
+        <v>2</v>
+      </c>
+      <c r="C46" s="102" t="s">
+        <v>3663</v>
+      </c>
+      <c r="D46" s="102" t="s">
         <v>63</v>
       </c>
-      <c r="C46" s="102" t="s">
-        <v>2</v>
-      </c>
-      <c r="D46" s="102" t="s">
+      <c r="E46" s="102" t="s">
         <v>3738</v>
-      </c>
-      <c r="E46" s="102" t="s">
-        <v>3663</v>
       </c>
       <c r="F46" s="102" t="s">
         <v>3973</v>
@@ -20620,16 +20624,16 @@
         <v>64</v>
       </c>
       <c r="B47" s="102" t="s">
+        <v>2</v>
+      </c>
+      <c r="C47" s="102" t="s">
+        <v>3663</v>
+      </c>
+      <c r="D47" s="102" t="s">
         <v>65</v>
       </c>
-      <c r="C47" s="102" t="s">
-        <v>2</v>
-      </c>
-      <c r="D47" s="102" t="s">
+      <c r="E47" s="102" t="s">
         <v>3739</v>
-      </c>
-      <c r="E47" s="102" t="s">
-        <v>3663</v>
       </c>
       <c r="F47" s="102" t="s">
         <v>3965</v>
@@ -20652,16 +20656,16 @@
         <v>66</v>
       </c>
       <c r="B48" s="102" t="s">
+        <v>2</v>
+      </c>
+      <c r="C48" s="102" t="s">
+        <v>3663</v>
+      </c>
+      <c r="D48" s="102" t="s">
         <v>67</v>
       </c>
-      <c r="C48" s="102" t="s">
-        <v>2</v>
-      </c>
-      <c r="D48" s="102" t="s">
+      <c r="E48" s="102" t="s">
         <v>3740</v>
-      </c>
-      <c r="E48" s="102" t="s">
-        <v>3663</v>
       </c>
       <c r="F48" s="102" t="s">
         <v>3975</v>
@@ -20684,16 +20688,16 @@
         <v>68</v>
       </c>
       <c r="B49" s="102" t="s">
+        <v>2</v>
+      </c>
+      <c r="C49" s="102" t="s">
+        <v>2174</v>
+      </c>
+      <c r="D49" s="102" t="s">
         <v>69</v>
       </c>
-      <c r="C49" s="102" t="s">
-        <v>2</v>
-      </c>
-      <c r="D49" s="102" t="s">
+      <c r="E49" s="102" t="s">
         <v>3741</v>
-      </c>
-      <c r="E49" s="102" t="s">
-        <v>2174</v>
       </c>
       <c r="F49" s="102"/>
       <c r="G49" s="102"/>
@@ -20708,16 +20712,16 @@
         <v>70</v>
       </c>
       <c r="B50" s="102" t="s">
+        <v>2</v>
+      </c>
+      <c r="C50" s="102" t="s">
+        <v>3663</v>
+      </c>
+      <c r="D50" s="102" t="s">
         <v>3742</v>
       </c>
-      <c r="C50" s="102" t="s">
-        <v>2</v>
-      </c>
-      <c r="D50" s="102" t="s">
+      <c r="E50" s="102" t="s">
         <v>3743</v>
-      </c>
-      <c r="E50" s="102" t="s">
-        <v>3663</v>
       </c>
       <c r="F50" s="102" t="s">
         <v>3978</v>
@@ -20740,16 +20744,16 @@
         <v>71</v>
       </c>
       <c r="B51" s="102" t="s">
+        <v>2</v>
+      </c>
+      <c r="C51" s="102" t="s">
+        <v>3663</v>
+      </c>
+      <c r="D51" s="102" t="s">
         <v>3744</v>
       </c>
-      <c r="C51" s="102" t="s">
-        <v>2</v>
-      </c>
-      <c r="D51" s="102" t="s">
+      <c r="E51" s="102" t="s">
         <v>3745</v>
-      </c>
-      <c r="E51" s="102" t="s">
-        <v>3663</v>
       </c>
       <c r="F51" s="102" t="s">
         <v>2107</v>
@@ -20772,16 +20776,16 @@
         <v>72</v>
       </c>
       <c r="B52" s="102" t="s">
+        <v>2</v>
+      </c>
+      <c r="C52" s="102" t="s">
+        <v>2174</v>
+      </c>
+      <c r="D52" s="102" t="s">
         <v>3746</v>
       </c>
-      <c r="C52" s="102" t="s">
-        <v>2</v>
-      </c>
-      <c r="D52" s="102" t="s">
+      <c r="E52" s="102" t="s">
         <v>3747</v>
-      </c>
-      <c r="E52" s="102" t="s">
-        <v>2174</v>
       </c>
       <c r="F52" s="102"/>
       <c r="G52" s="102"/>
@@ -20796,16 +20800,16 @@
         <v>73</v>
       </c>
       <c r="B53" s="102" t="s">
+        <v>2</v>
+      </c>
+      <c r="C53" s="102" t="s">
+        <v>2174</v>
+      </c>
+      <c r="D53" s="102" t="s">
         <v>74</v>
       </c>
-      <c r="C53" s="102" t="s">
-        <v>2</v>
-      </c>
-      <c r="D53" s="102" t="s">
+      <c r="E53" s="102" t="s">
         <v>3748</v>
-      </c>
-      <c r="E53" s="102" t="s">
-        <v>2174</v>
       </c>
       <c r="F53" s="102"/>
       <c r="G53" s="102"/>
@@ -20820,16 +20824,16 @@
         <v>75</v>
       </c>
       <c r="B54" s="102" t="s">
+        <v>2</v>
+      </c>
+      <c r="C54" s="102" t="s">
+        <v>3663</v>
+      </c>
+      <c r="D54" s="102" t="s">
         <v>3749</v>
       </c>
-      <c r="C54" s="102" t="s">
-        <v>2</v>
-      </c>
-      <c r="D54" s="102" t="s">
+      <c r="E54" s="102" t="s">
         <v>3750</v>
-      </c>
-      <c r="E54" s="102" t="s">
-        <v>3663</v>
       </c>
       <c r="F54" s="102" t="s">
         <v>1767</v>
@@ -20852,16 +20856,16 @@
         <v>76</v>
       </c>
       <c r="B55" s="102" t="s">
+        <v>2</v>
+      </c>
+      <c r="C55" s="102" t="s">
+        <v>3663</v>
+      </c>
+      <c r="D55" s="102" t="s">
         <v>77</v>
       </c>
-      <c r="C55" s="102" t="s">
-        <v>2</v>
-      </c>
-      <c r="D55" s="102" t="s">
+      <c r="E55" s="102" t="s">
         <v>3751</v>
-      </c>
-      <c r="E55" s="102" t="s">
-        <v>3663</v>
       </c>
       <c r="F55" s="102" t="s">
         <v>3984</v>
@@ -20884,16 +20888,16 @@
         <v>78</v>
       </c>
       <c r="B56" s="102" t="s">
+        <v>2</v>
+      </c>
+      <c r="C56" s="102" t="s">
+        <v>2174</v>
+      </c>
+      <c r="D56" s="102" t="s">
         <v>3752</v>
       </c>
-      <c r="C56" s="102" t="s">
-        <v>2</v>
-      </c>
-      <c r="D56" s="102" t="s">
+      <c r="E56" s="102" t="s">
         <v>3753</v>
-      </c>
-      <c r="E56" s="102" t="s">
-        <v>2174</v>
       </c>
       <c r="F56" s="102" t="s">
         <v>1566</v>
@@ -20916,16 +20920,16 @@
         <v>79</v>
       </c>
       <c r="B57" s="102" t="s">
+        <v>2</v>
+      </c>
+      <c r="C57" s="102" t="s">
+        <v>3663</v>
+      </c>
+      <c r="D57" s="102" t="s">
         <v>3754</v>
       </c>
-      <c r="C57" s="102" t="s">
-        <v>2</v>
-      </c>
-      <c r="D57" s="102" t="s">
+      <c r="E57" s="102" t="s">
         <v>3755</v>
-      </c>
-      <c r="E57" s="102" t="s">
-        <v>3663</v>
       </c>
       <c r="F57" s="102" t="s">
         <v>3988</v>
@@ -20948,16 +20952,16 @@
         <v>80</v>
       </c>
       <c r="B58" s="102" t="s">
+        <v>2</v>
+      </c>
+      <c r="C58" s="102" t="s">
+        <v>2174</v>
+      </c>
+      <c r="D58" s="102" t="s">
         <v>81</v>
       </c>
-      <c r="C58" s="102" t="s">
-        <v>2</v>
-      </c>
-      <c r="D58" s="102" t="s">
+      <c r="E58" s="102" t="s">
         <v>3756</v>
-      </c>
-      <c r="E58" s="102" t="s">
-        <v>2174</v>
       </c>
       <c r="F58" s="102"/>
       <c r="G58" s="102"/>
@@ -20972,16 +20976,16 @@
         <v>82</v>
       </c>
       <c r="B59" s="102" t="s">
+        <v>2</v>
+      </c>
+      <c r="C59" s="102" t="s">
+        <v>2174</v>
+      </c>
+      <c r="D59" s="102" t="s">
         <v>83</v>
       </c>
-      <c r="C59" s="102" t="s">
-        <v>2</v>
-      </c>
-      <c r="D59" s="102" t="s">
+      <c r="E59" s="102" t="s">
         <v>3757</v>
-      </c>
-      <c r="E59" s="102" t="s">
-        <v>2174</v>
       </c>
       <c r="F59" s="102"/>
       <c r="G59" s="102"/>
@@ -20996,16 +21000,16 @@
         <v>84</v>
       </c>
       <c r="B60" s="102" t="s">
+        <v>2</v>
+      </c>
+      <c r="C60" s="102" t="s">
+        <v>2174</v>
+      </c>
+      <c r="D60" s="102" t="s">
         <v>85</v>
       </c>
-      <c r="C60" s="102" t="s">
-        <v>2</v>
-      </c>
-      <c r="D60" s="102" t="s">
+      <c r="E60" s="102" t="s">
         <v>3758</v>
-      </c>
-      <c r="E60" s="102" t="s">
-        <v>2174</v>
       </c>
       <c r="F60" s="102"/>
       <c r="G60" s="102"/>
@@ -21020,16 +21024,16 @@
         <v>91</v>
       </c>
       <c r="B61" s="102" t="s">
+        <v>2</v>
+      </c>
+      <c r="C61" s="102" t="s">
+        <v>3663</v>
+      </c>
+      <c r="D61" s="102" t="s">
         <v>92</v>
       </c>
-      <c r="C61" s="102" t="s">
-        <v>2</v>
-      </c>
-      <c r="D61" s="102" t="s">
+      <c r="E61" s="102" t="s">
         <v>3759</v>
-      </c>
-      <c r="E61" s="102" t="s">
-        <v>3663</v>
       </c>
       <c r="F61" s="102" t="s">
         <v>3991</v>
@@ -21052,16 +21056,16 @@
         <v>101</v>
       </c>
       <c r="B62" s="102" t="s">
+        <v>2</v>
+      </c>
+      <c r="C62" s="102" t="s">
+        <v>3663</v>
+      </c>
+      <c r="D62" s="102" t="s">
         <v>102</v>
       </c>
-      <c r="C62" s="102" t="s">
-        <v>2</v>
-      </c>
-      <c r="D62" s="102" t="s">
+      <c r="E62" s="102" t="s">
         <v>3760</v>
-      </c>
-      <c r="E62" s="102" t="s">
-        <v>3663</v>
       </c>
       <c r="F62" s="102" t="s">
         <v>3993</v>
@@ -21084,16 +21088,16 @@
         <v>97</v>
       </c>
       <c r="B63" s="102" t="s">
+        <v>2</v>
+      </c>
+      <c r="C63" s="102" t="s">
+        <v>3660</v>
+      </c>
+      <c r="D63" s="102" t="s">
         <v>98</v>
       </c>
-      <c r="C63" s="102" t="s">
-        <v>2</v>
-      </c>
-      <c r="D63" s="102" t="s">
+      <c r="E63" s="102" t="s">
         <v>3761</v>
-      </c>
-      <c r="E63" s="102" t="s">
-        <v>3660</v>
       </c>
       <c r="F63" s="102" t="s">
         <v>3922</v>
@@ -21116,16 +21120,16 @@
         <v>86</v>
       </c>
       <c r="B64" s="102" t="s">
+        <v>2</v>
+      </c>
+      <c r="C64" s="102" t="s">
+        <v>2174</v>
+      </c>
+      <c r="D64" s="102" t="s">
         <v>87</v>
       </c>
-      <c r="C64" s="102" t="s">
-        <v>2</v>
-      </c>
-      <c r="D64" s="102" t="s">
+      <c r="E64" s="102" t="s">
         <v>3762</v>
-      </c>
-      <c r="E64" s="102" t="s">
-        <v>2174</v>
       </c>
       <c r="F64" s="102"/>
       <c r="G64" s="102"/>
@@ -21140,16 +21144,16 @@
         <v>88</v>
       </c>
       <c r="B65" s="102" t="s">
+        <v>2</v>
+      </c>
+      <c r="C65" s="102" t="s">
+        <v>3663</v>
+      </c>
+      <c r="D65" s="102" t="s">
         <v>89</v>
       </c>
-      <c r="C65" s="102" t="s">
-        <v>2</v>
-      </c>
-      <c r="D65" s="102" t="s">
+      <c r="E65" s="102" t="s">
         <v>3763</v>
-      </c>
-      <c r="E65" s="102" t="s">
-        <v>3663</v>
       </c>
       <c r="F65" s="102" t="s">
         <v>3997</v>
@@ -21172,16 +21176,16 @@
         <v>93</v>
       </c>
       <c r="B66" s="102" t="s">
+        <v>2</v>
+      </c>
+      <c r="C66" s="102" t="s">
+        <v>286</v>
+      </c>
+      <c r="D66" s="102" t="s">
         <v>94</v>
       </c>
-      <c r="C66" s="102" t="s">
-        <v>2</v>
-      </c>
-      <c r="D66" s="102" t="s">
+      <c r="E66" s="102" t="s">
         <v>3764</v>
-      </c>
-      <c r="E66" s="102" t="s">
-        <v>286</v>
       </c>
       <c r="F66" s="102" t="s">
         <v>1761</v>
@@ -21198,16 +21202,16 @@
         <v>95</v>
       </c>
       <c r="B67" s="102" t="s">
+        <v>2</v>
+      </c>
+      <c r="C67" s="102" t="s">
+        <v>2174</v>
+      </c>
+      <c r="D67" s="102" t="s">
         <v>96</v>
       </c>
-      <c r="C67" s="102" t="s">
-        <v>2</v>
-      </c>
-      <c r="D67" s="102" t="s">
+      <c r="E67" s="102" t="s">
         <v>3765</v>
-      </c>
-      <c r="E67" s="102" t="s">
-        <v>2174</v>
       </c>
       <c r="F67" s="102"/>
       <c r="G67" s="102"/>
@@ -21222,16 +21226,16 @@
         <v>103</v>
       </c>
       <c r="B68" s="102" t="s">
+        <v>2</v>
+      </c>
+      <c r="C68" s="102" t="s">
+        <v>2174</v>
+      </c>
+      <c r="D68" s="102" t="s">
         <v>104</v>
       </c>
-      <c r="C68" s="102" t="s">
-        <v>2</v>
-      </c>
-      <c r="D68" s="102" t="s">
+      <c r="E68" s="102" t="s">
         <v>3766</v>
-      </c>
-      <c r="E68" s="102" t="s">
-        <v>2174</v>
       </c>
       <c r="F68" s="102"/>
       <c r="G68" s="102"/>
@@ -21246,16 +21250,16 @@
         <v>105</v>
       </c>
       <c r="B69" s="102" t="s">
+        <v>2</v>
+      </c>
+      <c r="C69" s="102" t="s">
+        <v>3660</v>
+      </c>
+      <c r="D69" s="102" t="s">
         <v>106</v>
       </c>
-      <c r="C69" s="102" t="s">
-        <v>2</v>
-      </c>
-      <c r="D69" s="102" t="s">
+      <c r="E69" s="102" t="s">
         <v>3767</v>
-      </c>
-      <c r="E69" s="102" t="s">
-        <v>3660</v>
       </c>
       <c r="F69" s="102"/>
       <c r="G69" s="102"/>
@@ -21270,16 +21274,16 @@
         <v>90</v>
       </c>
       <c r="B70" s="102" t="s">
+        <v>2</v>
+      </c>
+      <c r="C70" s="102" t="s">
+        <v>3663</v>
+      </c>
+      <c r="D70" s="102" t="s">
         <v>3768</v>
       </c>
-      <c r="C70" s="102" t="s">
-        <v>2</v>
-      </c>
-      <c r="D70" s="102" t="s">
+      <c r="E70" s="102" t="s">
         <v>3769</v>
-      </c>
-      <c r="E70" s="102" t="s">
-        <v>3663</v>
       </c>
       <c r="F70" s="102" t="s">
         <v>4001</v>
@@ -21302,16 +21306,16 @@
         <v>99</v>
       </c>
       <c r="B71" s="102" t="s">
+        <v>2</v>
+      </c>
+      <c r="C71" s="102" t="s">
+        <v>2174</v>
+      </c>
+      <c r="D71" s="102" t="s">
         <v>100</v>
       </c>
-      <c r="C71" s="102" t="s">
-        <v>2</v>
-      </c>
-      <c r="D71" s="102" t="s">
+      <c r="E71" s="102" t="s">
         <v>3770</v>
-      </c>
-      <c r="E71" s="102" t="s">
-        <v>2174</v>
       </c>
       <c r="F71" s="102"/>
       <c r="G71" s="102"/>
@@ -21326,16 +21330,16 @@
         <v>107</v>
       </c>
       <c r="B72" s="102" t="s">
+        <v>2</v>
+      </c>
+      <c r="C72" s="102" t="s">
+        <v>2174</v>
+      </c>
+      <c r="D72" s="102" t="s">
         <v>3771</v>
       </c>
-      <c r="C72" s="102" t="s">
-        <v>2</v>
-      </c>
-      <c r="D72" s="102" t="s">
+      <c r="E72" s="102" t="s">
         <v>3772</v>
-      </c>
-      <c r="E72" s="102" t="s">
-        <v>2174</v>
       </c>
       <c r="F72" s="102"/>
       <c r="G72" s="102"/>
@@ -21350,16 +21354,16 @@
         <v>108</v>
       </c>
       <c r="B73" s="102" t="s">
+        <v>2</v>
+      </c>
+      <c r="C73" s="102" t="s">
+        <v>3663</v>
+      </c>
+      <c r="D73" s="102" t="s">
         <v>109</v>
       </c>
-      <c r="C73" s="102" t="s">
-        <v>2</v>
-      </c>
-      <c r="D73" s="102" t="s">
+      <c r="E73" s="102" t="s">
         <v>3773</v>
-      </c>
-      <c r="E73" s="102" t="s">
-        <v>3663</v>
       </c>
       <c r="F73" s="102" t="s">
         <v>4004</v>
@@ -21382,16 +21386,16 @@
         <v>110</v>
       </c>
       <c r="B74" s="102" t="s">
+        <v>2</v>
+      </c>
+      <c r="C74" s="102" t="s">
+        <v>3663</v>
+      </c>
+      <c r="D74" s="102" t="s">
         <v>3774</v>
       </c>
-      <c r="C74" s="102" t="s">
-        <v>2</v>
-      </c>
-      <c r="D74" s="102" t="s">
+      <c r="E74" s="102" t="s">
         <v>3775</v>
-      </c>
-      <c r="E74" s="102" t="s">
-        <v>3663</v>
       </c>
       <c r="F74" s="102" t="s">
         <v>4008</v>
@@ -21414,16 +21418,16 @@
         <v>111</v>
       </c>
       <c r="B75" s="102" t="s">
+        <v>2</v>
+      </c>
+      <c r="C75" s="102" t="s">
+        <v>3663</v>
+      </c>
+      <c r="D75" s="102" t="s">
         <v>112</v>
       </c>
-      <c r="C75" s="102" t="s">
-        <v>2</v>
-      </c>
-      <c r="D75" s="102" t="s">
+      <c r="E75" s="102" t="s">
         <v>3776</v>
-      </c>
-      <c r="E75" s="102" t="s">
-        <v>3663</v>
       </c>
       <c r="F75" s="102" t="s">
         <v>1561</v>
@@ -21446,16 +21450,16 @@
         <v>113</v>
       </c>
       <c r="B76" s="102" t="s">
+        <v>2</v>
+      </c>
+      <c r="C76" s="102" t="s">
+        <v>2174</v>
+      </c>
+      <c r="D76" s="102" t="s">
         <v>114</v>
       </c>
-      <c r="C76" s="102" t="s">
-        <v>2</v>
-      </c>
-      <c r="D76" s="102" t="s">
+      <c r="E76" s="102" t="s">
         <v>3777</v>
-      </c>
-      <c r="E76" s="102" t="s">
-        <v>2174</v>
       </c>
       <c r="F76" s="102"/>
       <c r="G76" s="102"/>
@@ -21470,16 +21474,16 @@
         <v>121</v>
       </c>
       <c r="B77" s="102" t="s">
+        <v>2</v>
+      </c>
+      <c r="C77" s="102" t="s">
+        <v>2174</v>
+      </c>
+      <c r="D77" s="102" t="s">
         <v>122</v>
       </c>
-      <c r="C77" s="102" t="s">
-        <v>2</v>
-      </c>
-      <c r="D77" s="102" t="s">
+      <c r="E77" s="102" t="s">
         <v>3778</v>
-      </c>
-      <c r="E77" s="102" t="s">
-        <v>2174</v>
       </c>
       <c r="F77" s="102"/>
       <c r="G77" s="102"/>
@@ -21494,16 +21498,16 @@
         <v>117</v>
       </c>
       <c r="B78" s="102" t="s">
+        <v>2</v>
+      </c>
+      <c r="C78" s="102" t="s">
+        <v>3663</v>
+      </c>
+      <c r="D78" s="102" t="s">
         <v>118</v>
       </c>
-      <c r="C78" s="102" t="s">
-        <v>2</v>
-      </c>
-      <c r="D78" s="102" t="s">
+      <c r="E78" s="102" t="s">
         <v>3779</v>
-      </c>
-      <c r="E78" s="102" t="s">
-        <v>3663</v>
       </c>
       <c r="F78" s="102" t="s">
         <v>4012</v>
@@ -21526,16 +21530,16 @@
         <v>119</v>
       </c>
       <c r="B79" s="102" t="s">
+        <v>2</v>
+      </c>
+      <c r="C79" s="102" t="s">
+        <v>3663</v>
+      </c>
+      <c r="D79" s="102" t="s">
         <v>120</v>
       </c>
-      <c r="C79" s="102" t="s">
-        <v>2</v>
-      </c>
-      <c r="D79" s="102" t="s">
+      <c r="E79" s="102" t="s">
         <v>3780</v>
-      </c>
-      <c r="E79" s="102" t="s">
-        <v>3663</v>
       </c>
       <c r="F79" s="102" t="s">
         <v>4012</v>
@@ -21558,16 +21562,16 @@
         <v>115</v>
       </c>
       <c r="B80" s="102" t="s">
+        <v>2</v>
+      </c>
+      <c r="C80" s="102" t="s">
+        <v>3663</v>
+      </c>
+      <c r="D80" s="102" t="s">
         <v>116</v>
       </c>
-      <c r="C80" s="102" t="s">
-        <v>2</v>
-      </c>
-      <c r="D80" s="102" t="s">
+      <c r="E80" s="102" t="s">
         <v>3781</v>
-      </c>
-      <c r="E80" s="102" t="s">
-        <v>3663</v>
       </c>
       <c r="F80" s="102" t="s">
         <v>2107</v>
@@ -21590,16 +21594,16 @@
         <v>123</v>
       </c>
       <c r="B81" s="102" t="s">
+        <v>2</v>
+      </c>
+      <c r="C81" s="102" t="s">
+        <v>2174</v>
+      </c>
+      <c r="D81" s="102" t="s">
         <v>124</v>
       </c>
-      <c r="C81" s="102" t="s">
-        <v>2</v>
-      </c>
-      <c r="D81" s="102" t="s">
+      <c r="E81" s="102" t="s">
         <v>3782</v>
-      </c>
-      <c r="E81" s="102" t="s">
-        <v>2174</v>
       </c>
       <c r="F81" s="102"/>
       <c r="G81" s="102"/>
@@ -21614,16 +21618,16 @@
         <v>125</v>
       </c>
       <c r="B82" s="102" t="s">
+        <v>2</v>
+      </c>
+      <c r="C82" s="102" t="s">
+        <v>2174</v>
+      </c>
+      <c r="D82" s="102" t="s">
         <v>126</v>
       </c>
-      <c r="C82" s="102" t="s">
-        <v>2</v>
-      </c>
-      <c r="D82" s="102" t="s">
+      <c r="E82" s="102" t="s">
         <v>3783</v>
-      </c>
-      <c r="E82" s="102" t="s">
-        <v>2174</v>
       </c>
       <c r="F82" s="102"/>
       <c r="G82" s="102"/>
@@ -21638,16 +21642,16 @@
         <v>127</v>
       </c>
       <c r="B83" s="102" t="s">
+        <v>2</v>
+      </c>
+      <c r="C83" s="102" t="s">
+        <v>3663</v>
+      </c>
+      <c r="D83" s="102" t="s">
         <v>3784</v>
       </c>
-      <c r="C83" s="102" t="s">
-        <v>2</v>
-      </c>
-      <c r="D83" s="102" t="s">
+      <c r="E83" s="102" t="s">
         <v>3785</v>
-      </c>
-      <c r="E83" s="102" t="s">
-        <v>3663</v>
       </c>
       <c r="F83" s="102" t="s">
         <v>4016</v>
@@ -21670,16 +21674,16 @@
         <v>128</v>
       </c>
       <c r="B84" s="102" t="s">
+        <v>2</v>
+      </c>
+      <c r="C84" s="102" t="s">
+        <v>3663</v>
+      </c>
+      <c r="D84" s="102" t="s">
         <v>129</v>
       </c>
-      <c r="C84" s="102" t="s">
-        <v>2</v>
-      </c>
-      <c r="D84" s="102" t="s">
+      <c r="E84" s="102" t="s">
         <v>3786</v>
-      </c>
-      <c r="E84" s="102" t="s">
-        <v>3663</v>
       </c>
       <c r="F84" s="102" t="s">
         <v>4020</v>
@@ -21702,16 +21706,16 @@
         <v>130</v>
       </c>
       <c r="B85" s="102" t="s">
+        <v>2</v>
+      </c>
+      <c r="C85" s="102" t="s">
+        <v>3663</v>
+      </c>
+      <c r="D85" s="102" t="s">
         <v>3787</v>
       </c>
-      <c r="C85" s="102" t="s">
-        <v>2</v>
-      </c>
-      <c r="D85" s="102" t="s">
+      <c r="E85" s="102" t="s">
         <v>3788</v>
-      </c>
-      <c r="E85" s="102" t="s">
-        <v>3663</v>
       </c>
       <c r="F85" s="102" t="s">
         <v>1561</v>
@@ -21734,16 +21738,16 @@
         <v>131</v>
       </c>
       <c r="B86" s="102" t="s">
+        <v>2</v>
+      </c>
+      <c r="C86" s="102" t="s">
+        <v>3663</v>
+      </c>
+      <c r="D86" s="102" t="s">
         <v>3789</v>
       </c>
-      <c r="C86" s="102" t="s">
-        <v>2</v>
-      </c>
-      <c r="D86" s="102" t="s">
+      <c r="E86" s="102" t="s">
         <v>3790</v>
-      </c>
-      <c r="E86" s="102" t="s">
-        <v>3663</v>
       </c>
       <c r="F86" s="102" t="s">
         <v>4023</v>
@@ -21766,16 +21770,16 @@
         <v>132</v>
       </c>
       <c r="B87" s="102" t="s">
+        <v>2</v>
+      </c>
+      <c r="C87" s="102" t="s">
+        <v>3663</v>
+      </c>
+      <c r="D87" s="102" t="s">
         <v>133</v>
       </c>
-      <c r="C87" s="102" t="s">
-        <v>2</v>
-      </c>
-      <c r="D87" s="102" t="s">
+      <c r="E87" s="102" t="s">
         <v>3791</v>
-      </c>
-      <c r="E87" s="102" t="s">
-        <v>3663</v>
       </c>
       <c r="F87" s="102" t="s">
         <v>4026</v>
@@ -21798,16 +21802,16 @@
         <v>138</v>
       </c>
       <c r="B88" s="102" t="s">
+        <v>2</v>
+      </c>
+      <c r="C88" s="102" t="s">
+        <v>286</v>
+      </c>
+      <c r="D88" s="102" t="s">
         <v>3792</v>
       </c>
-      <c r="C88" s="102" t="s">
-        <v>2</v>
-      </c>
-      <c r="D88" s="102" t="s">
+      <c r="E88" s="102" t="s">
         <v>3793</v>
-      </c>
-      <c r="E88" s="102" t="s">
-        <v>286</v>
       </c>
       <c r="F88" s="102"/>
       <c r="G88" s="102"/>
@@ -21822,16 +21826,16 @@
         <v>139</v>
       </c>
       <c r="B89" s="102" t="s">
+        <v>2</v>
+      </c>
+      <c r="C89" s="102" t="s">
+        <v>3663</v>
+      </c>
+      <c r="D89" s="102" t="s">
         <v>3794</v>
       </c>
-      <c r="C89" s="102" t="s">
-        <v>2</v>
-      </c>
-      <c r="D89" s="102" t="s">
+      <c r="E89" s="102" t="s">
         <v>3795</v>
-      </c>
-      <c r="E89" s="102" t="s">
-        <v>3663</v>
       </c>
       <c r="F89" s="102" t="s">
         <v>4030</v>
@@ -21854,16 +21858,16 @@
         <v>134</v>
       </c>
       <c r="B90" s="102" t="s">
+        <v>2</v>
+      </c>
+      <c r="C90" s="102" t="s">
+        <v>2174</v>
+      </c>
+      <c r="D90" s="102" t="s">
         <v>3796</v>
       </c>
-      <c r="C90" s="102" t="s">
-        <v>2</v>
-      </c>
-      <c r="D90" s="102" t="s">
+      <c r="E90" s="102" t="s">
         <v>3797</v>
-      </c>
-      <c r="E90" s="102" t="s">
-        <v>2174</v>
       </c>
       <c r="F90" s="102" t="s">
         <v>1566</v>
@@ -21886,16 +21890,16 @@
         <v>135</v>
       </c>
       <c r="B91" s="102" t="s">
+        <v>2</v>
+      </c>
+      <c r="C91" s="102" t="s">
+        <v>3663</v>
+      </c>
+      <c r="D91" s="102" t="s">
         <v>136</v>
       </c>
-      <c r="C91" s="102" t="s">
-        <v>2</v>
-      </c>
-      <c r="D91" s="102" t="s">
+      <c r="E91" s="102" t="s">
         <v>3798</v>
-      </c>
-      <c r="E91" s="102" t="s">
-        <v>3663</v>
       </c>
       <c r="F91" s="102" t="s">
         <v>4012</v>
@@ -21918,16 +21922,16 @@
         <v>137</v>
       </c>
       <c r="B92" s="102" t="s">
+        <v>2</v>
+      </c>
+      <c r="C92" s="102" t="s">
+        <v>286</v>
+      </c>
+      <c r="D92" s="102" t="s">
         <v>3799</v>
       </c>
-      <c r="C92" s="102" t="s">
-        <v>2</v>
-      </c>
-      <c r="D92" s="102" t="s">
+      <c r="E92" s="102" t="s">
         <v>3800</v>
-      </c>
-      <c r="E92" s="102" t="s">
-        <v>286</v>
       </c>
       <c r="F92" s="102"/>
       <c r="G92" s="102"/>
@@ -21942,16 +21946,16 @@
         <v>140</v>
       </c>
       <c r="B93" s="102" t="s">
+        <v>2</v>
+      </c>
+      <c r="C93" s="102" t="s">
+        <v>3663</v>
+      </c>
+      <c r="D93" s="102" t="s">
         <v>3801</v>
       </c>
-      <c r="C93" s="102" t="s">
-        <v>2</v>
-      </c>
-      <c r="D93" s="102" t="s">
+      <c r="E93" s="102" t="s">
         <v>3802</v>
-      </c>
-      <c r="E93" s="102" t="s">
-        <v>3663</v>
       </c>
       <c r="F93" s="102" t="s">
         <v>4032</v>
@@ -21974,16 +21978,16 @@
         <v>141</v>
       </c>
       <c r="B94" s="102" t="s">
+        <v>3</v>
+      </c>
+      <c r="C94" s="102" t="s">
+        <v>3663</v>
+      </c>
+      <c r="D94" s="102" t="s">
         <v>3803</v>
       </c>
-      <c r="C94" s="102" t="s">
-        <v>3</v>
-      </c>
-      <c r="D94" s="102" t="s">
+      <c r="E94" s="102" t="s">
         <v>3804</v>
-      </c>
-      <c r="E94" s="102" t="s">
-        <v>3663</v>
       </c>
       <c r="F94" s="102" t="s">
         <v>1565</v>
@@ -22002,16 +22006,16 @@
         <v>142</v>
       </c>
       <c r="B95" s="102" t="s">
+        <v>3</v>
+      </c>
+      <c r="C95" s="102" t="s">
+        <v>3663</v>
+      </c>
+      <c r="D95" s="102" t="s">
         <v>3805</v>
       </c>
-      <c r="C95" s="102" t="s">
-        <v>3</v>
-      </c>
-      <c r="D95" s="102" t="s">
+      <c r="E95" s="102" t="s">
         <v>3806</v>
-      </c>
-      <c r="E95" s="102" t="s">
-        <v>3663</v>
       </c>
       <c r="F95" s="102" t="s">
         <v>4035</v>
@@ -22034,16 +22038,16 @@
         <v>143</v>
       </c>
       <c r="B96" s="102" t="s">
+        <v>3</v>
+      </c>
+      <c r="C96" s="102" t="s">
+        <v>3663</v>
+      </c>
+      <c r="D96" s="102" t="s">
         <v>3807</v>
       </c>
-      <c r="C96" s="102" t="s">
-        <v>3</v>
-      </c>
-      <c r="D96" s="102" t="s">
+      <c r="E96" s="102" t="s">
         <v>3808</v>
-      </c>
-      <c r="E96" s="102" t="s">
-        <v>3663</v>
       </c>
       <c r="F96" s="102" t="s">
         <v>4039</v>
@@ -22066,16 +22070,16 @@
         <v>144</v>
       </c>
       <c r="B97" s="102" t="s">
+        <v>3</v>
+      </c>
+      <c r="C97" s="102" t="s">
+        <v>3663</v>
+      </c>
+      <c r="D97" s="102" t="s">
         <v>145</v>
       </c>
-      <c r="C97" s="102" t="s">
-        <v>3</v>
-      </c>
-      <c r="D97" s="102" t="s">
+      <c r="E97" s="102" t="s">
         <v>3809</v>
-      </c>
-      <c r="E97" s="102" t="s">
-        <v>3663</v>
       </c>
       <c r="F97" s="102" t="s">
         <v>4039</v>
@@ -22098,16 +22102,16 @@
         <v>146</v>
       </c>
       <c r="B98" s="102" t="s">
+        <v>3</v>
+      </c>
+      <c r="C98" s="102" t="s">
+        <v>3663</v>
+      </c>
+      <c r="D98" s="102" t="s">
         <v>147</v>
       </c>
-      <c r="C98" s="102" t="s">
-        <v>3</v>
-      </c>
-      <c r="D98" s="102" t="s">
+      <c r="E98" s="102" t="s">
         <v>3810</v>
-      </c>
-      <c r="E98" s="102" t="s">
-        <v>3663</v>
       </c>
       <c r="F98" s="102" t="s">
         <v>4041</v>
@@ -22130,16 +22134,16 @@
         <v>148</v>
       </c>
       <c r="B99" s="102" t="s">
+        <v>3</v>
+      </c>
+      <c r="C99" s="102" t="s">
+        <v>3663</v>
+      </c>
+      <c r="D99" s="102" t="s">
         <v>149</v>
       </c>
-      <c r="C99" s="102" t="s">
-        <v>3</v>
-      </c>
-      <c r="D99" s="102" t="s">
+      <c r="E99" s="102" t="s">
         <v>3811</v>
-      </c>
-      <c r="E99" s="102" t="s">
-        <v>3663</v>
       </c>
       <c r="F99" s="102" t="s">
         <v>4035</v>
@@ -22162,16 +22166,16 @@
         <v>150</v>
       </c>
       <c r="B100" s="102" t="s">
+        <v>3</v>
+      </c>
+      <c r="C100" s="102" t="s">
+        <v>3663</v>
+      </c>
+      <c r="D100" s="102" t="s">
         <v>3812</v>
       </c>
-      <c r="C100" s="102" t="s">
-        <v>3</v>
-      </c>
-      <c r="D100" s="102" t="s">
+      <c r="E100" s="102" t="s">
         <v>3813</v>
-      </c>
-      <c r="E100" s="102" t="s">
-        <v>3663</v>
       </c>
       <c r="F100" s="102" t="s">
         <v>1532</v>
@@ -22194,16 +22198,16 @@
         <v>155</v>
       </c>
       <c r="B101" s="102" t="s">
+        <v>3</v>
+      </c>
+      <c r="C101" s="102" t="s">
+        <v>3663</v>
+      </c>
+      <c r="D101" s="102" t="s">
         <v>156</v>
       </c>
-      <c r="C101" s="102" t="s">
-        <v>3</v>
-      </c>
-      <c r="D101" s="102" t="s">
+      <c r="E101" s="102" t="s">
         <v>3814</v>
-      </c>
-      <c r="E101" s="102" t="s">
-        <v>3663</v>
       </c>
       <c r="F101" s="102" t="s">
         <v>4044</v>
@@ -22226,16 +22230,16 @@
         <v>151</v>
       </c>
       <c r="B102" s="102" t="s">
+        <v>3</v>
+      </c>
+      <c r="C102" s="102" t="s">
+        <v>2174</v>
+      </c>
+      <c r="D102" s="102" t="s">
         <v>3815</v>
       </c>
-      <c r="C102" s="102" t="s">
-        <v>3</v>
-      </c>
-      <c r="D102" s="102" t="s">
+      <c r="E102" s="102" t="s">
         <v>3816</v>
-      </c>
-      <c r="E102" s="102" t="s">
-        <v>2174</v>
       </c>
       <c r="F102" s="102" t="s">
         <v>1566</v>
@@ -22258,16 +22262,16 @@
         <v>152</v>
       </c>
       <c r="B103" s="102" t="s">
+        <v>3</v>
+      </c>
+      <c r="C103" s="102" t="s">
+        <v>3663</v>
+      </c>
+      <c r="D103" s="102" t="s">
         <v>3817</v>
       </c>
-      <c r="C103" s="102" t="s">
-        <v>3</v>
-      </c>
-      <c r="D103" s="102" t="s">
+      <c r="E103" s="102" t="s">
         <v>3818</v>
-      </c>
-      <c r="E103" s="102" t="s">
-        <v>3663</v>
       </c>
       <c r="F103" s="102" t="s">
         <v>1532</v>
@@ -22290,16 +22294,16 @@
         <v>153</v>
       </c>
       <c r="B104" s="102" t="s">
+        <v>3</v>
+      </c>
+      <c r="C104" s="102" t="s">
+        <v>3663</v>
+      </c>
+      <c r="D104" s="102" t="s">
         <v>3819</v>
       </c>
-      <c r="C104" s="102" t="s">
-        <v>3</v>
-      </c>
-      <c r="D104" s="102" t="s">
+      <c r="E104" s="102" t="s">
         <v>3820</v>
-      </c>
-      <c r="E104" s="102" t="s">
-        <v>3663</v>
       </c>
       <c r="F104" s="102" t="s">
         <v>4047</v>
@@ -22322,16 +22326,16 @@
         <v>157</v>
       </c>
       <c r="B105" s="102" t="s">
+        <v>3</v>
+      </c>
+      <c r="C105" s="102" t="s">
+        <v>3663</v>
+      </c>
+      <c r="D105" s="102" t="s">
         <v>3821</v>
       </c>
-      <c r="C105" s="102" t="s">
-        <v>3</v>
-      </c>
-      <c r="D105" s="102" t="s">
+      <c r="E105" s="102" t="s">
         <v>3822</v>
-      </c>
-      <c r="E105" s="102" t="s">
-        <v>3663</v>
       </c>
       <c r="F105" s="102" t="s">
         <v>4049</v>
@@ -22354,16 +22358,16 @@
         <v>158</v>
       </c>
       <c r="B106" s="102" t="s">
+        <v>3</v>
+      </c>
+      <c r="C106" s="102" t="s">
+        <v>3663</v>
+      </c>
+      <c r="D106" s="102" t="s">
         <v>159</v>
       </c>
-      <c r="C106" s="102" t="s">
-        <v>3</v>
-      </c>
-      <c r="D106" s="102" t="s">
+      <c r="E106" s="102" t="s">
         <v>3823</v>
-      </c>
-      <c r="E106" s="102" t="s">
-        <v>3663</v>
       </c>
       <c r="F106" s="102" t="s">
         <v>4050</v>
@@ -22386,16 +22390,16 @@
         <v>154</v>
       </c>
       <c r="B107" s="102" t="s">
+        <v>3</v>
+      </c>
+      <c r="C107" s="102" t="s">
+        <v>3663</v>
+      </c>
+      <c r="D107" s="102" t="s">
         <v>3824</v>
       </c>
-      <c r="C107" s="102" t="s">
-        <v>3</v>
-      </c>
-      <c r="D107" s="102" t="s">
+      <c r="E107" s="102" t="s">
         <v>3825</v>
-      </c>
-      <c r="E107" s="102" t="s">
-        <v>3663</v>
       </c>
       <c r="F107" s="102" t="s">
         <v>4053</v>
@@ -22416,16 +22420,16 @@
         <v>160</v>
       </c>
       <c r="B108" s="102" t="s">
+        <v>3</v>
+      </c>
+      <c r="C108" s="102" t="s">
+        <v>3663</v>
+      </c>
+      <c r="D108" s="102" t="s">
         <v>3826</v>
       </c>
-      <c r="C108" s="102" t="s">
-        <v>3</v>
-      </c>
-      <c r="D108" s="102" t="s">
+      <c r="E108" s="102" t="s">
         <v>3827</v>
-      </c>
-      <c r="E108" s="102" t="s">
-        <v>3663</v>
       </c>
       <c r="F108" s="102" t="s">
         <v>4056</v>
@@ -22448,16 +22452,16 @@
         <v>161</v>
       </c>
       <c r="B109" s="102" t="s">
+        <v>3</v>
+      </c>
+      <c r="C109" s="102" t="s">
+        <v>3663</v>
+      </c>
+      <c r="D109" s="102" t="s">
         <v>162</v>
       </c>
-      <c r="C109" s="102" t="s">
-        <v>3</v>
-      </c>
-      <c r="D109" s="102" t="s">
+      <c r="E109" s="102" t="s">
         <v>3828</v>
-      </c>
-      <c r="E109" s="102" t="s">
-        <v>3663</v>
       </c>
       <c r="F109" s="102" t="s">
         <v>4056</v>
@@ -22480,16 +22484,16 @@
         <v>163</v>
       </c>
       <c r="B110" s="102" t="s">
+        <v>3</v>
+      </c>
+      <c r="C110" s="102" t="s">
+        <v>3663</v>
+      </c>
+      <c r="D110" s="102" t="s">
         <v>3829</v>
       </c>
-      <c r="C110" s="102" t="s">
-        <v>3</v>
-      </c>
-      <c r="D110" s="102" t="s">
+      <c r="E110" s="102" t="s">
         <v>3830</v>
-      </c>
-      <c r="E110" s="102" t="s">
-        <v>3663</v>
       </c>
       <c r="F110" s="102" t="s">
         <v>4057</v>
@@ -22512,16 +22516,16 @@
         <v>164</v>
       </c>
       <c r="B111" s="102" t="s">
+        <v>3</v>
+      </c>
+      <c r="C111" s="102" t="s">
+        <v>3663</v>
+      </c>
+      <c r="D111" s="102" t="s">
         <v>3831</v>
       </c>
-      <c r="C111" s="102" t="s">
-        <v>3</v>
-      </c>
-      <c r="D111" s="102" t="s">
+      <c r="E111" s="102" t="s">
         <v>3832</v>
-      </c>
-      <c r="E111" s="102" t="s">
-        <v>3663</v>
       </c>
       <c r="F111" s="102" t="s">
         <v>1766</v>
@@ -22542,16 +22546,16 @@
         <v>165</v>
       </c>
       <c r="B112" s="102" t="s">
+        <v>3</v>
+      </c>
+      <c r="C112" s="102" t="s">
+        <v>3663</v>
+      </c>
+      <c r="D112" s="102" t="s">
         <v>166</v>
       </c>
-      <c r="C112" s="102" t="s">
-        <v>3</v>
-      </c>
-      <c r="D112" s="102" t="s">
+      <c r="E112" s="102" t="s">
         <v>3833</v>
-      </c>
-      <c r="E112" s="102" t="s">
-        <v>3663</v>
       </c>
       <c r="F112" s="102" t="s">
         <v>4039</v>
@@ -22574,16 +22578,16 @@
         <v>167</v>
       </c>
       <c r="B113" s="102" t="s">
+        <v>3</v>
+      </c>
+      <c r="C113" s="102" t="s">
+        <v>286</v>
+      </c>
+      <c r="D113" s="102" t="s">
         <v>3834</v>
       </c>
-      <c r="C113" s="102" t="s">
-        <v>3</v>
-      </c>
-      <c r="D113" s="102" t="s">
+      <c r="E113" s="102" t="s">
         <v>3835</v>
-      </c>
-      <c r="E113" s="102" t="s">
-        <v>286</v>
       </c>
       <c r="F113" s="102"/>
       <c r="G113" s="102"/>
@@ -22598,16 +22602,16 @@
         <v>168</v>
       </c>
       <c r="B114" s="102" t="s">
+        <v>3</v>
+      </c>
+      <c r="C114" s="102" t="s">
+        <v>3663</v>
+      </c>
+      <c r="D114" s="102" t="s">
         <v>169</v>
       </c>
-      <c r="C114" s="102" t="s">
-        <v>3</v>
-      </c>
-      <c r="D114" s="102" t="s">
+      <c r="E114" s="102" t="s">
         <v>3836</v>
-      </c>
-      <c r="E114" s="102" t="s">
-        <v>3663</v>
       </c>
       <c r="F114" s="102" t="s">
         <v>4053</v>
@@ -22628,16 +22632,16 @@
         <v>170</v>
       </c>
       <c r="B115" s="102" t="s">
+        <v>3</v>
+      </c>
+      <c r="C115" s="102" t="s">
+        <v>3663</v>
+      </c>
+      <c r="D115" s="102" t="s">
         <v>171</v>
       </c>
-      <c r="C115" s="102" t="s">
-        <v>3</v>
-      </c>
-      <c r="D115" s="102" t="s">
+      <c r="E115" s="102" t="s">
         <v>3837</v>
-      </c>
-      <c r="E115" s="102" t="s">
-        <v>3663</v>
       </c>
       <c r="F115" s="102" t="s">
         <v>4059</v>
@@ -22660,16 +22664,16 @@
         <v>172</v>
       </c>
       <c r="B116" s="102" t="s">
+        <v>3</v>
+      </c>
+      <c r="C116" s="102" t="s">
+        <v>3663</v>
+      </c>
+      <c r="D116" s="102" t="s">
         <v>173</v>
       </c>
-      <c r="C116" s="102" t="s">
-        <v>3</v>
-      </c>
-      <c r="D116" s="102" t="s">
+      <c r="E116" s="102" t="s">
         <v>3838</v>
-      </c>
-      <c r="E116" s="102" t="s">
-        <v>3663</v>
       </c>
       <c r="F116" s="102" t="s">
         <v>4062</v>
@@ -22692,16 +22696,16 @@
         <v>174</v>
       </c>
       <c r="B117" s="102" t="s">
+        <v>3</v>
+      </c>
+      <c r="C117" s="102" t="s">
+        <v>3663</v>
+      </c>
+      <c r="D117" s="102" t="s">
         <v>175</v>
       </c>
-      <c r="C117" s="102" t="s">
-        <v>3</v>
-      </c>
-      <c r="D117" s="102" t="s">
+      <c r="E117" s="102" t="s">
         <v>3839</v>
-      </c>
-      <c r="E117" s="102" t="s">
-        <v>3663</v>
       </c>
       <c r="F117" s="102" t="s">
         <v>4063</v>
@@ -22724,16 +22728,16 @@
         <v>180</v>
       </c>
       <c r="B118" s="102" t="s">
+        <v>3</v>
+      </c>
+      <c r="C118" s="102" t="s">
+        <v>3663</v>
+      </c>
+      <c r="D118" s="102" t="s">
         <v>181</v>
       </c>
-      <c r="C118" s="102" t="s">
-        <v>3</v>
-      </c>
-      <c r="D118" s="102" t="s">
+      <c r="E118" s="102" t="s">
         <v>3840</v>
-      </c>
-      <c r="E118" s="102" t="s">
-        <v>3663</v>
       </c>
       <c r="F118" s="102" t="s">
         <v>3978</v>
@@ -22756,16 +22760,16 @@
         <v>182</v>
       </c>
       <c r="B119" s="102" t="s">
+        <v>3</v>
+      </c>
+      <c r="C119" s="102" t="s">
+        <v>3663</v>
+      </c>
+      <c r="D119" s="102" t="s">
         <v>183</v>
       </c>
-      <c r="C119" s="102" t="s">
-        <v>3</v>
-      </c>
-      <c r="D119" s="102" t="s">
+      <c r="E119" s="102" t="s">
         <v>3841</v>
-      </c>
-      <c r="E119" s="102" t="s">
-        <v>3663</v>
       </c>
       <c r="F119" s="102" t="s">
         <v>3965</v>
@@ -22788,16 +22792,16 @@
         <v>184</v>
       </c>
       <c r="B120" s="102" t="s">
+        <v>3</v>
+      </c>
+      <c r="C120" s="102" t="s">
+        <v>3663</v>
+      </c>
+      <c r="D120" s="102" t="s">
         <v>185</v>
       </c>
-      <c r="C120" s="102" t="s">
-        <v>3</v>
-      </c>
-      <c r="D120" s="102" t="s">
+      <c r="E120" s="102" t="s">
         <v>3842</v>
-      </c>
-      <c r="E120" s="102" t="s">
-        <v>3663</v>
       </c>
       <c r="F120" s="102" t="s">
         <v>3978</v>
@@ -22820,16 +22824,16 @@
         <v>186</v>
       </c>
       <c r="B121" s="102" t="s">
+        <v>3</v>
+      </c>
+      <c r="C121" s="102" t="s">
+        <v>3663</v>
+      </c>
+      <c r="D121" s="102" t="s">
         <v>187</v>
       </c>
-      <c r="C121" s="102" t="s">
-        <v>3</v>
-      </c>
-      <c r="D121" s="102" t="s">
+      <c r="E121" s="102" t="s">
         <v>3843</v>
-      </c>
-      <c r="E121" s="102" t="s">
-        <v>3663</v>
       </c>
       <c r="F121" s="102" t="s">
         <v>3965</v>
@@ -22852,16 +22856,16 @@
         <v>188</v>
       </c>
       <c r="B122" s="102" t="s">
+        <v>3</v>
+      </c>
+      <c r="C122" s="102" t="s">
+        <v>3663</v>
+      </c>
+      <c r="D122" s="102" t="s">
         <v>189</v>
       </c>
-      <c r="C122" s="102" t="s">
-        <v>3</v>
-      </c>
-      <c r="D122" s="102" t="s">
+      <c r="E122" s="102" t="s">
         <v>3844</v>
-      </c>
-      <c r="E122" s="102" t="s">
-        <v>3663</v>
       </c>
       <c r="F122" s="102" t="s">
         <v>1763</v>
@@ -22884,16 +22888,16 @@
         <v>176</v>
       </c>
       <c r="B123" s="102" t="s">
+        <v>3</v>
+      </c>
+      <c r="C123" s="102" t="s">
+        <v>3660</v>
+      </c>
+      <c r="D123" s="102" t="s">
         <v>177</v>
       </c>
-      <c r="C123" s="102" t="s">
-        <v>3</v>
-      </c>
-      <c r="D123" s="102" t="s">
+      <c r="E123" s="102" t="s">
         <v>3845</v>
-      </c>
-      <c r="E123" s="102" t="s">
-        <v>3660</v>
       </c>
       <c r="F123" s="102" t="s">
         <v>3922</v>
@@ -22916,16 +22920,16 @@
         <v>192</v>
       </c>
       <c r="B124" s="102" t="s">
+        <v>3</v>
+      </c>
+      <c r="C124" s="102" t="s">
+        <v>3663</v>
+      </c>
+      <c r="D124" s="102" t="s">
         <v>193</v>
       </c>
-      <c r="C124" s="102" t="s">
-        <v>3</v>
-      </c>
-      <c r="D124" s="102" t="s">
+      <c r="E124" s="102" t="s">
         <v>3846</v>
-      </c>
-      <c r="E124" s="102" t="s">
-        <v>3663</v>
       </c>
       <c r="F124" s="102" t="s">
         <v>1755</v>
@@ -22948,16 +22952,16 @@
         <v>199</v>
       </c>
       <c r="B125" s="102" t="s">
+        <v>3</v>
+      </c>
+      <c r="C125" s="102" t="s">
+        <v>286</v>
+      </c>
+      <c r="D125" s="102" t="s">
         <v>3847</v>
       </c>
-      <c r="C125" s="102" t="s">
-        <v>3</v>
-      </c>
-      <c r="D125" s="102" t="s">
+      <c r="E125" s="102" t="s">
         <v>3848</v>
-      </c>
-      <c r="E125" s="102" t="s">
-        <v>286</v>
       </c>
       <c r="F125" s="102"/>
       <c r="G125" s="102"/>
@@ -22972,16 +22976,16 @@
         <v>194</v>
       </c>
       <c r="B126" s="102" t="s">
+        <v>3</v>
+      </c>
+      <c r="C126" s="102" t="s">
+        <v>286</v>
+      </c>
+      <c r="D126" s="102" t="s">
         <v>3849</v>
       </c>
-      <c r="C126" s="102" t="s">
-        <v>3</v>
-      </c>
-      <c r="D126" s="102" t="s">
+      <c r="E126" s="102" t="s">
         <v>3850</v>
-      </c>
-      <c r="E126" s="102" t="s">
-        <v>286</v>
       </c>
       <c r="F126" s="102"/>
       <c r="G126" s="102"/>
@@ -22996,16 +23000,16 @@
         <v>195</v>
       </c>
       <c r="B127" s="102" t="s">
+        <v>3</v>
+      </c>
+      <c r="C127" s="102" t="s">
+        <v>3663</v>
+      </c>
+      <c r="D127" s="102" t="s">
         <v>196</v>
       </c>
-      <c r="C127" s="102" t="s">
-        <v>3</v>
-      </c>
-      <c r="D127" s="102" t="s">
+      <c r="E127" s="102" t="s">
         <v>3851</v>
-      </c>
-      <c r="E127" s="102" t="s">
-        <v>3663</v>
       </c>
       <c r="F127" s="102" t="s">
         <v>4068</v>
@@ -23028,16 +23032,16 @@
         <v>197</v>
       </c>
       <c r="B128" s="102" t="s">
+        <v>3</v>
+      </c>
+      <c r="C128" s="102" t="s">
+        <v>3663</v>
+      </c>
+      <c r="D128" s="102" t="s">
         <v>198</v>
       </c>
-      <c r="C128" s="102" t="s">
-        <v>3</v>
-      </c>
-      <c r="D128" s="102" t="s">
+      <c r="E128" s="102" t="s">
         <v>3852</v>
-      </c>
-      <c r="E128" s="102" t="s">
-        <v>3663</v>
       </c>
       <c r="F128" s="102" t="s">
         <v>4035</v>
@@ -23060,16 +23064,16 @@
         <v>178</v>
       </c>
       <c r="B129" s="102" t="s">
+        <v>3</v>
+      </c>
+      <c r="C129" s="102" t="s">
+        <v>3663</v>
+      </c>
+      <c r="D129" s="102" t="s">
         <v>179</v>
       </c>
-      <c r="C129" s="102" t="s">
-        <v>3</v>
-      </c>
-      <c r="D129" s="102" t="s">
+      <c r="E129" s="102" t="s">
         <v>3853</v>
-      </c>
-      <c r="E129" s="102" t="s">
-        <v>3663</v>
       </c>
       <c r="F129" s="102" t="s">
         <v>4070</v>
@@ -23092,16 +23096,16 @@
         <v>200</v>
       </c>
       <c r="B130" s="102" t="s">
+        <v>3</v>
+      </c>
+      <c r="C130" s="102" t="s">
+        <v>3663</v>
+      </c>
+      <c r="D130" s="102" t="s">
         <v>201</v>
       </c>
-      <c r="C130" s="102" t="s">
-        <v>3</v>
-      </c>
-      <c r="D130" s="102" t="s">
+      <c r="E130" s="102" t="s">
         <v>3854</v>
-      </c>
-      <c r="E130" s="102" t="s">
-        <v>3663</v>
       </c>
       <c r="F130" s="102" t="s">
         <v>4074</v>
@@ -23124,16 +23128,16 @@
         <v>202</v>
       </c>
       <c r="B131" s="102" t="s">
+        <v>3</v>
+      </c>
+      <c r="C131" s="102" t="s">
+        <v>3663</v>
+      </c>
+      <c r="D131" s="102" t="s">
         <v>203</v>
       </c>
-      <c r="C131" s="102" t="s">
-        <v>3</v>
-      </c>
-      <c r="D131" s="102" t="s">
+      <c r="E131" s="102" t="s">
         <v>3855</v>
-      </c>
-      <c r="E131" s="102" t="s">
-        <v>3663</v>
       </c>
       <c r="F131" s="102" t="s">
         <v>4076</v>
@@ -23156,16 +23160,16 @@
         <v>204</v>
       </c>
       <c r="B132" s="102" t="s">
+        <v>3</v>
+      </c>
+      <c r="C132" s="102" t="s">
+        <v>3663</v>
+      </c>
+      <c r="D132" s="102" t="s">
         <v>3856</v>
       </c>
-      <c r="C132" s="102" t="s">
-        <v>3</v>
-      </c>
-      <c r="D132" s="102" t="s">
+      <c r="E132" s="102" t="s">
         <v>3857</v>
-      </c>
-      <c r="E132" s="102" t="s">
-        <v>3663</v>
       </c>
       <c r="F132" s="102" t="s">
         <v>4068</v>
@@ -23188,16 +23192,16 @@
         <v>205</v>
       </c>
       <c r="B133" s="102" t="s">
+        <v>3</v>
+      </c>
+      <c r="C133" s="102" t="s">
+        <v>3663</v>
+      </c>
+      <c r="D133" s="102" t="s">
         <v>3858</v>
       </c>
-      <c r="C133" s="102" t="s">
-        <v>3</v>
-      </c>
-      <c r="D133" s="102" t="s">
+      <c r="E133" s="102" t="s">
         <v>3859</v>
-      </c>
-      <c r="E133" s="102" t="s">
-        <v>3663</v>
       </c>
       <c r="F133" s="102" t="s">
         <v>4074</v>
@@ -23220,16 +23224,16 @@
         <v>190</v>
       </c>
       <c r="B134" s="102" t="s">
+        <v>3</v>
+      </c>
+      <c r="C134" s="102" t="s">
+        <v>3663</v>
+      </c>
+      <c r="D134" s="102" t="s">
         <v>191</v>
       </c>
-      <c r="C134" s="102" t="s">
-        <v>3</v>
-      </c>
-      <c r="D134" s="102" t="s">
+      <c r="E134" s="102" t="s">
         <v>3860</v>
-      </c>
-      <c r="E134" s="102" t="s">
-        <v>3663</v>
       </c>
       <c r="F134" s="102" t="s">
         <v>3965</v>
@@ -23252,16 +23256,16 @@
         <v>206</v>
       </c>
       <c r="B135" s="102" t="s">
+        <v>3</v>
+      </c>
+      <c r="C135" s="102" t="s">
+        <v>3663</v>
+      </c>
+      <c r="D135" s="102" t="s">
         <v>207</v>
       </c>
-      <c r="C135" s="102" t="s">
-        <v>3</v>
-      </c>
-      <c r="D135" s="102" t="s">
+      <c r="E135" s="102" t="s">
         <v>3861</v>
-      </c>
-      <c r="E135" s="102" t="s">
-        <v>3663</v>
       </c>
       <c r="F135" s="102" t="s">
         <v>4080</v>
@@ -23284,16 +23288,16 @@
         <v>208</v>
       </c>
       <c r="B136" s="102" t="s">
+        <v>3</v>
+      </c>
+      <c r="C136" s="102" t="s">
+        <v>3663</v>
+      </c>
+      <c r="D136" s="102" t="s">
         <v>209</v>
       </c>
-      <c r="C136" s="102" t="s">
-        <v>3</v>
-      </c>
-      <c r="D136" s="102" t="s">
+      <c r="E136" s="102" t="s">
         <v>3862</v>
-      </c>
-      <c r="E136" s="102" t="s">
-        <v>3663</v>
       </c>
       <c r="F136" s="102" t="s">
         <v>4080</v>
@@ -23316,16 +23320,16 @@
         <v>210</v>
       </c>
       <c r="B137" s="102" t="s">
+        <v>3</v>
+      </c>
+      <c r="C137" s="102" t="s">
+        <v>3663</v>
+      </c>
+      <c r="D137" s="102" t="s">
         <v>211</v>
       </c>
-      <c r="C137" s="102" t="s">
-        <v>3</v>
-      </c>
-      <c r="D137" s="102" t="s">
+      <c r="E137" s="102" t="s">
         <v>3863</v>
-      </c>
-      <c r="E137" s="102" t="s">
-        <v>3663</v>
       </c>
       <c r="F137" s="102" t="s">
         <v>4085</v>
@@ -23348,16 +23352,16 @@
         <v>212</v>
       </c>
       <c r="B138" s="102" t="s">
+        <v>3</v>
+      </c>
+      <c r="C138" s="102" t="s">
+        <v>3663</v>
+      </c>
+      <c r="D138" s="102" t="s">
         <v>213</v>
       </c>
-      <c r="C138" s="102" t="s">
-        <v>3</v>
-      </c>
-      <c r="D138" s="102" t="s">
+      <c r="E138" s="102" t="s">
         <v>3864</v>
-      </c>
-      <c r="E138" s="102" t="s">
-        <v>3663</v>
       </c>
       <c r="F138" s="102" t="s">
         <v>1510</v>
@@ -23380,16 +23384,16 @@
         <v>214</v>
       </c>
       <c r="B139" s="102" t="s">
+        <v>3</v>
+      </c>
+      <c r="C139" s="102" t="s">
+        <v>3663</v>
+      </c>
+      <c r="D139" s="102" t="s">
         <v>215</v>
       </c>
-      <c r="C139" s="102" t="s">
-        <v>3</v>
-      </c>
-      <c r="D139" s="102" t="s">
+      <c r="E139" s="102" t="s">
         <v>3865</v>
-      </c>
-      <c r="E139" s="102" t="s">
-        <v>3663</v>
       </c>
       <c r="F139" s="102" t="s">
         <v>1510</v>
@@ -23412,16 +23416,16 @@
         <v>216</v>
       </c>
       <c r="B140" s="102" t="s">
+        <v>3</v>
+      </c>
+      <c r="C140" s="102" t="s">
+        <v>3663</v>
+      </c>
+      <c r="D140" s="102" t="s">
         <v>217</v>
       </c>
-      <c r="C140" s="102" t="s">
-        <v>3</v>
-      </c>
-      <c r="D140" s="102" t="s">
+      <c r="E140" s="102" t="s">
         <v>3866</v>
-      </c>
-      <c r="E140" s="102" t="s">
-        <v>3663</v>
       </c>
       <c r="F140" s="102" t="s">
         <v>4085</v>
@@ -23444,16 +23448,16 @@
         <v>218</v>
       </c>
       <c r="B141" s="102" t="s">
+        <v>3</v>
+      </c>
+      <c r="C141" s="102" t="s">
+        <v>3663</v>
+      </c>
+      <c r="D141" s="102" t="s">
         <v>3867</v>
       </c>
-      <c r="C141" s="102" t="s">
-        <v>3</v>
-      </c>
-      <c r="D141" s="102" t="s">
+      <c r="E141" s="102" t="s">
         <v>3868</v>
-      </c>
-      <c r="E141" s="102" t="s">
-        <v>3663</v>
       </c>
       <c r="F141" s="102" t="s">
         <v>4085</v>
@@ -23476,16 +23480,16 @@
         <v>219</v>
       </c>
       <c r="B142" s="102" t="s">
+        <v>3</v>
+      </c>
+      <c r="C142" s="102" t="s">
+        <v>3663</v>
+      </c>
+      <c r="D142" s="102" t="s">
         <v>3869</v>
       </c>
-      <c r="C142" s="102" t="s">
-        <v>3</v>
-      </c>
-      <c r="D142" s="102" t="s">
+      <c r="E142" s="102" t="s">
         <v>3870</v>
-      </c>
-      <c r="E142" s="102" t="s">
-        <v>3663</v>
       </c>
       <c r="F142" s="102" t="s">
         <v>4085</v>
@@ -23508,16 +23512,16 @@
         <v>220</v>
       </c>
       <c r="B143" s="102" t="s">
+        <v>3</v>
+      </c>
+      <c r="C143" s="102" t="s">
+        <v>3663</v>
+      </c>
+      <c r="D143" s="102" t="s">
         <v>221</v>
       </c>
-      <c r="C143" s="102" t="s">
-        <v>3</v>
-      </c>
-      <c r="D143" s="102" t="s">
+      <c r="E143" s="102" t="s">
         <v>3871</v>
-      </c>
-      <c r="E143" s="102" t="s">
-        <v>3663</v>
       </c>
       <c r="F143" s="102" t="s">
         <v>4088</v>
@@ -23540,16 +23544,16 @@
         <v>222</v>
       </c>
       <c r="B144" s="102" t="s">
+        <v>3</v>
+      </c>
+      <c r="C144" s="102" t="s">
+        <v>3663</v>
+      </c>
+      <c r="D144" s="102" t="s">
         <v>223</v>
       </c>
-      <c r="C144" s="102" t="s">
-        <v>3</v>
-      </c>
-      <c r="D144" s="102" t="s">
+      <c r="E144" s="102" t="s">
         <v>3872</v>
-      </c>
-      <c r="E144" s="102" t="s">
-        <v>3663</v>
       </c>
       <c r="F144" s="102" t="s">
         <v>4088</v>
@@ -23572,16 +23576,16 @@
         <v>224</v>
       </c>
       <c r="B145" s="102" t="s">
+        <v>3</v>
+      </c>
+      <c r="C145" s="102" t="s">
+        <v>3663</v>
+      </c>
+      <c r="D145" s="102" t="s">
         <v>225</v>
       </c>
-      <c r="C145" s="102" t="s">
-        <v>3</v>
-      </c>
-      <c r="D145" s="102" t="s">
+      <c r="E145" s="102" t="s">
         <v>3873</v>
-      </c>
-      <c r="E145" s="102" t="s">
-        <v>3663</v>
       </c>
       <c r="F145" s="102" t="s">
         <v>4012</v>
@@ -23604,16 +23608,16 @@
         <v>226</v>
       </c>
       <c r="B146" s="102" t="s">
+        <v>3</v>
+      </c>
+      <c r="C146" s="102" t="s">
+        <v>3663</v>
+      </c>
+      <c r="D146" s="102" t="s">
         <v>227</v>
       </c>
-      <c r="C146" s="102" t="s">
-        <v>3</v>
-      </c>
-      <c r="D146" s="102" t="s">
+      <c r="E146" s="102" t="s">
         <v>3874</v>
-      </c>
-      <c r="E146" s="102" t="s">
-        <v>3663</v>
       </c>
       <c r="F146" s="102" t="s">
         <v>4012</v>
@@ -23636,16 +23640,16 @@
         <v>228</v>
       </c>
       <c r="B147" s="102" t="s">
+        <v>3</v>
+      </c>
+      <c r="C147" s="102" t="s">
+        <v>3663</v>
+      </c>
+      <c r="D147" s="102" t="s">
         <v>229</v>
       </c>
-      <c r="C147" s="102" t="s">
-        <v>3</v>
-      </c>
-      <c r="D147" s="102" t="s">
+      <c r="E147" s="102" t="s">
         <v>3875</v>
-      </c>
-      <c r="E147" s="102" t="s">
-        <v>3663</v>
       </c>
       <c r="F147" s="102" t="s">
         <v>4035</v>
@@ -23668,16 +23672,16 @@
         <v>230</v>
       </c>
       <c r="B148" s="102" t="s">
+        <v>3</v>
+      </c>
+      <c r="C148" s="102" t="s">
+        <v>3663</v>
+      </c>
+      <c r="D148" s="102" t="s">
         <v>3876</v>
       </c>
-      <c r="C148" s="102" t="s">
-        <v>3</v>
-      </c>
-      <c r="D148" s="102" t="s">
+      <c r="E148" s="102" t="s">
         <v>3877</v>
-      </c>
-      <c r="E148" s="102" t="s">
-        <v>3663</v>
       </c>
       <c r="F148" s="102" t="s">
         <v>4035</v>
@@ -23700,16 +23704,16 @@
         <v>231</v>
       </c>
       <c r="B149" s="102" t="s">
+        <v>3</v>
+      </c>
+      <c r="C149" s="102" t="s">
+        <v>3663</v>
+      </c>
+      <c r="D149" s="102" t="s">
         <v>3878</v>
       </c>
-      <c r="C149" s="102" t="s">
-        <v>3</v>
-      </c>
-      <c r="D149" s="102" t="s">
+      <c r="E149" s="102" t="s">
         <v>3879</v>
-      </c>
-      <c r="E149" s="102" t="s">
-        <v>3663</v>
       </c>
       <c r="F149" s="102" t="s">
         <v>4090</v>
@@ -23726,16 +23730,16 @@
         <v>234</v>
       </c>
       <c r="B150" s="102" t="s">
+        <v>3</v>
+      </c>
+      <c r="C150" s="102" t="s">
+        <v>3663</v>
+      </c>
+      <c r="D150" s="102" t="s">
         <v>3880</v>
       </c>
-      <c r="C150" s="102" t="s">
-        <v>3</v>
-      </c>
-      <c r="D150" s="102" t="s">
+      <c r="E150" s="102" t="s">
         <v>3881</v>
-      </c>
-      <c r="E150" s="102" t="s">
-        <v>3663</v>
       </c>
       <c r="F150" s="102" t="s">
         <v>4091</v>
@@ -23756,16 +23760,16 @@
         <v>235</v>
       </c>
       <c r="B151" s="102" t="s">
+        <v>3</v>
+      </c>
+      <c r="C151" s="102" t="s">
+        <v>3663</v>
+      </c>
+      <c r="D151" s="102" t="s">
         <v>236</v>
       </c>
-      <c r="C151" s="102" t="s">
-        <v>3</v>
-      </c>
-      <c r="D151" s="102" t="s">
+      <c r="E151" s="102" t="s">
         <v>3882</v>
-      </c>
-      <c r="E151" s="102" t="s">
-        <v>3663</v>
       </c>
       <c r="F151" s="102" t="s">
         <v>4093</v>
@@ -23782,16 +23786,16 @@
         <v>232</v>
       </c>
       <c r="B152" s="102" t="s">
+        <v>3</v>
+      </c>
+      <c r="C152" s="102" t="s">
+        <v>3663</v>
+      </c>
+      <c r="D152" s="102" t="s">
         <v>233</v>
       </c>
-      <c r="C152" s="102" t="s">
-        <v>3</v>
-      </c>
-      <c r="D152" s="102" t="s">
+      <c r="E152" s="102" t="s">
         <v>3883</v>
-      </c>
-      <c r="E152" s="102" t="s">
-        <v>3663</v>
       </c>
       <c r="F152" s="102" t="s">
         <v>4032</v>
@@ -23814,16 +23818,16 @@
         <v>237</v>
       </c>
       <c r="B153" s="102" t="s">
+        <v>3</v>
+      </c>
+      <c r="C153" s="102" t="s">
+        <v>3663</v>
+      </c>
+      <c r="D153" s="102" t="s">
         <v>3884</v>
       </c>
-      <c r="C153" s="102" t="s">
-        <v>3</v>
-      </c>
-      <c r="D153" s="102" t="s">
+      <c r="E153" s="102" t="s">
         <v>3885</v>
-      </c>
-      <c r="E153" s="102" t="s">
-        <v>3663</v>
       </c>
       <c r="F153" s="102" t="s">
         <v>4094</v>
@@ -23844,16 +23848,16 @@
         <v>238</v>
       </c>
       <c r="B154" s="102" t="s">
+        <v>3</v>
+      </c>
+      <c r="C154" s="102" t="s">
+        <v>3663</v>
+      </c>
+      <c r="D154" s="102" t="s">
         <v>239</v>
       </c>
-      <c r="C154" s="102" t="s">
-        <v>3</v>
-      </c>
-      <c r="D154" s="102" t="s">
+      <c r="E154" s="102" t="s">
         <v>3886</v>
-      </c>
-      <c r="E154" s="102" t="s">
-        <v>3663</v>
       </c>
       <c r="F154" s="102" t="s">
         <v>1500</v>
@@ -23876,16 +23880,16 @@
         <v>240</v>
       </c>
       <c r="B155" s="102" t="s">
+        <v>3</v>
+      </c>
+      <c r="C155" s="102" t="s">
+        <v>286</v>
+      </c>
+      <c r="D155" s="102" t="s">
         <v>241</v>
       </c>
-      <c r="C155" s="102" t="s">
-        <v>3</v>
-      </c>
-      <c r="D155" s="102" t="s">
+      <c r="E155" s="102" t="s">
         <v>3887</v>
-      </c>
-      <c r="E155" s="102" t="s">
-        <v>286</v>
       </c>
       <c r="F155" s="102"/>
       <c r="G155" s="102"/>
@@ -23900,16 +23904,16 @@
         <v>244</v>
       </c>
       <c r="B156" s="102" t="s">
+        <v>3</v>
+      </c>
+      <c r="C156" s="102" t="s">
+        <v>286</v>
+      </c>
+      <c r="D156" s="102" t="s">
         <v>245</v>
       </c>
-      <c r="C156" s="102" t="s">
-        <v>3</v>
-      </c>
-      <c r="D156" s="102" t="s">
+      <c r="E156" s="102" t="s">
         <v>3888</v>
-      </c>
-      <c r="E156" s="102" t="s">
-        <v>286</v>
       </c>
       <c r="F156" s="102"/>
       <c r="G156" s="102"/>
@@ -23924,16 +23928,16 @@
         <v>246</v>
       </c>
       <c r="B157" s="102" t="s">
+        <v>3</v>
+      </c>
+      <c r="C157" s="102" t="s">
+        <v>286</v>
+      </c>
+      <c r="D157" s="102" t="s">
         <v>247</v>
       </c>
-      <c r="C157" s="102" t="s">
-        <v>3</v>
-      </c>
-      <c r="D157" s="102" t="s">
+      <c r="E157" s="102" t="s">
         <v>3889</v>
-      </c>
-      <c r="E157" s="102" t="s">
-        <v>286</v>
       </c>
       <c r="F157" s="102"/>
       <c r="G157" s="102"/>
@@ -23948,16 +23952,16 @@
         <v>248</v>
       </c>
       <c r="B158" s="102" t="s">
+        <v>3</v>
+      </c>
+      <c r="C158" s="102" t="s">
+        <v>286</v>
+      </c>
+      <c r="D158" s="102" t="s">
         <v>3890</v>
       </c>
-      <c r="C158" s="102" t="s">
-        <v>3</v>
-      </c>
-      <c r="D158" s="102" t="s">
+      <c r="E158" s="102" t="s">
         <v>3891</v>
-      </c>
-      <c r="E158" s="102" t="s">
-        <v>286</v>
       </c>
       <c r="F158" s="102"/>
       <c r="G158" s="102"/>
@@ -23972,16 +23976,16 @@
         <v>249</v>
       </c>
       <c r="B159" s="102" t="s">
+        <v>3</v>
+      </c>
+      <c r="C159" s="102" t="s">
+        <v>286</v>
+      </c>
+      <c r="D159" s="102" t="s">
         <v>3892</v>
       </c>
-      <c r="C159" s="102" t="s">
-        <v>3</v>
-      </c>
-      <c r="D159" s="102" t="s">
+      <c r="E159" s="102" t="s">
         <v>3893</v>
-      </c>
-      <c r="E159" s="102" t="s">
-        <v>286</v>
       </c>
       <c r="F159" s="102"/>
       <c r="G159" s="102"/>
@@ -23998,16 +24002,16 @@
         <v>250</v>
       </c>
       <c r="B160" s="102" t="s">
+        <v>3</v>
+      </c>
+      <c r="C160" s="102" t="s">
+        <v>3663</v>
+      </c>
+      <c r="D160" s="102" t="s">
         <v>3894</v>
       </c>
-      <c r="C160" s="102" t="s">
-        <v>3</v>
-      </c>
-      <c r="D160" s="102" t="s">
+      <c r="E160" s="102" t="s">
         <v>3895</v>
-      </c>
-      <c r="E160" s="102" t="s">
-        <v>3663</v>
       </c>
       <c r="F160" s="102" t="s">
         <v>4012</v>
@@ -24030,16 +24034,16 @@
         <v>242</v>
       </c>
       <c r="B161" s="102" t="s">
+        <v>3</v>
+      </c>
+      <c r="C161" s="102" t="s">
+        <v>3663</v>
+      </c>
+      <c r="D161" s="102" t="s">
         <v>243</v>
       </c>
-      <c r="C161" s="102" t="s">
-        <v>3</v>
-      </c>
-      <c r="D161" s="102" t="s">
+      <c r="E161" s="102" t="s">
         <v>3896</v>
-      </c>
-      <c r="E161" s="102" t="s">
-        <v>3663</v>
       </c>
       <c r="F161" s="102" t="s">
         <v>1523</v>
@@ -24062,16 +24066,16 @@
         <v>253</v>
       </c>
       <c r="B162" s="102" t="s">
+        <v>3</v>
+      </c>
+      <c r="C162" s="102" t="s">
+        <v>3663</v>
+      </c>
+      <c r="D162" s="102" t="s">
         <v>3897</v>
       </c>
-      <c r="C162" s="102" t="s">
-        <v>3</v>
-      </c>
-      <c r="D162" s="102" t="s">
+      <c r="E162" s="102" t="s">
         <v>3898</v>
-      </c>
-      <c r="E162" s="102" t="s">
-        <v>3663</v>
       </c>
       <c r="F162" s="102" t="s">
         <v>1567</v>
@@ -24094,16 +24098,16 @@
         <v>251</v>
       </c>
       <c r="B163" s="102" t="s">
+        <v>3</v>
+      </c>
+      <c r="C163" s="102" t="s">
+        <v>3663</v>
+      </c>
+      <c r="D163" s="102" t="s">
         <v>252</v>
       </c>
-      <c r="C163" s="102" t="s">
-        <v>3</v>
-      </c>
-      <c r="D163" s="102" t="s">
+      <c r="E163" s="102" t="s">
         <v>3899</v>
-      </c>
-      <c r="E163" s="102" t="s">
-        <v>3663</v>
       </c>
       <c r="F163" s="102" t="s">
         <v>4012</v>
@@ -24126,16 +24130,16 @@
         <v>254</v>
       </c>
       <c r="B164" s="102" t="s">
+        <v>3</v>
+      </c>
+      <c r="C164" s="102" t="s">
+        <v>3663</v>
+      </c>
+      <c r="D164" s="102" t="s">
         <v>3900</v>
       </c>
-      <c r="C164" s="102" t="s">
-        <v>3</v>
-      </c>
-      <c r="D164" s="102" t="s">
+      <c r="E164" s="102" t="s">
         <v>3901</v>
-      </c>
-      <c r="E164" s="102" t="s">
-        <v>3663</v>
       </c>
       <c r="F164" s="102" t="s">
         <v>4097</v>
@@ -24158,16 +24162,16 @@
         <v>255</v>
       </c>
       <c r="B165" s="102" t="s">
+        <v>3</v>
+      </c>
+      <c r="C165" s="102" t="s">
+        <v>3663</v>
+      </c>
+      <c r="D165" s="102" t="s">
         <v>256</v>
       </c>
-      <c r="C165" s="102" t="s">
-        <v>3</v>
-      </c>
-      <c r="D165" s="102" t="s">
+      <c r="E165" s="102" t="s">
         <v>3902</v>
-      </c>
-      <c r="E165" s="102" t="s">
-        <v>3663</v>
       </c>
       <c r="F165" s="102"/>
       <c r="G165" s="102"/>
@@ -24182,16 +24186,16 @@
         <v>257</v>
       </c>
       <c r="B166" s="102" t="s">
+        <v>3</v>
+      </c>
+      <c r="C166" s="102" t="s">
+        <v>3663</v>
+      </c>
+      <c r="D166" s="102" t="s">
         <v>258</v>
       </c>
-      <c r="C166" s="102" t="s">
-        <v>3</v>
-      </c>
-      <c r="D166" s="102" t="s">
+      <c r="E166" s="102" t="s">
         <v>3903</v>
-      </c>
-      <c r="E166" s="102" t="s">
-        <v>3663</v>
       </c>
       <c r="F166" s="102"/>
       <c r="G166" s="102"/>
@@ -24206,16 +24210,16 @@
         <v>259</v>
       </c>
       <c r="B167" s="102" t="s">
+        <v>3</v>
+      </c>
+      <c r="C167" s="102" t="s">
+        <v>3663</v>
+      </c>
+      <c r="D167" s="102" t="s">
         <v>3904</v>
       </c>
-      <c r="C167" s="102" t="s">
-        <v>3</v>
-      </c>
-      <c r="D167" s="102" t="s">
+      <c r="E167" s="102" t="s">
         <v>3905</v>
-      </c>
-      <c r="E167" s="102" t="s">
-        <v>3663</v>
       </c>
       <c r="F167" s="102"/>
       <c r="G167" s="102"/>
@@ -24230,16 +24234,16 @@
         <v>260</v>
       </c>
       <c r="B168" s="102" t="s">
+        <v>3</v>
+      </c>
+      <c r="C168" s="102" t="s">
+        <v>3663</v>
+      </c>
+      <c r="D168" s="102" t="s">
         <v>3906</v>
       </c>
-      <c r="C168" s="102" t="s">
-        <v>3</v>
-      </c>
-      <c r="D168" s="102" t="s">
+      <c r="E168" s="102" t="s">
         <v>3907</v>
-      </c>
-      <c r="E168" s="102" t="s">
-        <v>3663</v>
       </c>
       <c r="F168" s="102" t="s">
         <v>4085</v>
@@ -24262,16 +24266,16 @@
         <v>261</v>
       </c>
       <c r="B169" s="102" t="s">
+        <v>3</v>
+      </c>
+      <c r="C169" s="102" t="s">
+        <v>3663</v>
+      </c>
+      <c r="D169" s="102" t="s">
         <v>262</v>
       </c>
-      <c r="C169" s="102" t="s">
-        <v>3</v>
-      </c>
-      <c r="D169" s="102" t="s">
+      <c r="E169" s="102" t="s">
         <v>3908</v>
-      </c>
-      <c r="E169" s="102" t="s">
-        <v>3663</v>
       </c>
       <c r="F169" s="102" t="s">
         <v>4093</v>
@@ -24288,16 +24292,16 @@
         <v>263</v>
       </c>
       <c r="B170" s="102" t="s">
+        <v>3</v>
+      </c>
+      <c r="C170" s="102" t="s">
+        <v>3663</v>
+      </c>
+      <c r="D170" s="102" t="s">
         <v>3909</v>
       </c>
-      <c r="C170" s="102" t="s">
-        <v>3</v>
-      </c>
-      <c r="D170" s="102" t="s">
+      <c r="E170" s="102" t="s">
         <v>3910</v>
-      </c>
-      <c r="E170" s="102" t="s">
-        <v>3663</v>
       </c>
       <c r="F170" s="102" t="s">
         <v>4035</v>
@@ -24320,16 +24324,16 @@
         <v>264</v>
       </c>
       <c r="B171" s="102" t="s">
+        <v>3</v>
+      </c>
+      <c r="C171" s="102" t="s">
+        <v>3663</v>
+      </c>
+      <c r="D171" s="102" t="s">
         <v>3911</v>
       </c>
-      <c r="C171" s="102" t="s">
-        <v>3</v>
-      </c>
-      <c r="D171" s="102" t="s">
+      <c r="E171" s="102" t="s">
         <v>3912</v>
-      </c>
-      <c r="E171" s="102" t="s">
-        <v>3663</v>
       </c>
       <c r="F171" s="102"/>
       <c r="G171" s="102"/>
@@ -24344,16 +24348,16 @@
         <v>265</v>
       </c>
       <c r="B172" s="102" t="s">
+        <v>3</v>
+      </c>
+      <c r="C172" s="102" t="s">
+        <v>3663</v>
+      </c>
+      <c r="D172" s="102" t="s">
         <v>3913</v>
       </c>
-      <c r="C172" s="102" t="s">
-        <v>3</v>
-      </c>
-      <c r="D172" s="102" t="s">
+      <c r="E172" s="102" t="s">
         <v>3914</v>
-      </c>
-      <c r="E172" s="102" t="s">
-        <v>3663</v>
       </c>
       <c r="F172" s="102"/>
       <c r="G172" s="102"/>
@@ -24368,16 +24372,16 @@
         <v>266</v>
       </c>
       <c r="B173" s="102" t="s">
+        <v>3</v>
+      </c>
+      <c r="C173" s="102" t="s">
+        <v>3663</v>
+      </c>
+      <c r="D173" s="102" t="s">
         <v>3915</v>
       </c>
-      <c r="C173" s="102" t="s">
-        <v>3</v>
-      </c>
-      <c r="D173" s="102" t="s">
+      <c r="E173" s="102" t="s">
         <v>3916</v>
-      </c>
-      <c r="E173" s="102" t="s">
-        <v>3663</v>
       </c>
       <c r="F173" s="102"/>
       <c r="G173" s="102"/>
@@ -24392,16 +24396,16 @@
         <v>267</v>
       </c>
       <c r="B174" s="102" t="s">
+        <v>3</v>
+      </c>
+      <c r="C174" s="102" t="s">
+        <v>2174</v>
+      </c>
+      <c r="D174" s="102" t="s">
         <v>268</v>
       </c>
-      <c r="C174" s="102" t="s">
-        <v>3</v>
-      </c>
-      <c r="D174" s="102" t="s">
+      <c r="E174" s="102" t="s">
         <v>3917</v>
-      </c>
-      <c r="E174" s="102" t="s">
-        <v>2174</v>
       </c>
       <c r="F174" s="102"/>
       <c r="G174" s="102"/>
@@ -24416,16 +24420,16 @@
         <v>269</v>
       </c>
       <c r="B175" s="102" t="s">
+        <v>3</v>
+      </c>
+      <c r="C175" s="102" t="s">
+        <v>2174</v>
+      </c>
+      <c r="D175" s="102" t="s">
         <v>270</v>
       </c>
-      <c r="C175" s="102" t="s">
-        <v>3</v>
-      </c>
-      <c r="D175" s="102" t="s">
+      <c r="E175" s="102" t="s">
         <v>3918</v>
-      </c>
-      <c r="E175" s="102" t="s">
-        <v>2174</v>
       </c>
       <c r="F175" s="102"/>
       <c r="G175" s="102"/>
@@ -24440,16 +24444,16 @@
         <v>271</v>
       </c>
       <c r="B176" s="102" t="s">
+        <v>3</v>
+      </c>
+      <c r="C176" s="102" t="s">
+        <v>3663</v>
+      </c>
+      <c r="D176" s="102" t="s">
         <v>272</v>
       </c>
-      <c r="C176" s="102" t="s">
-        <v>3</v>
-      </c>
-      <c r="D176" s="102" t="s">
+      <c r="E176" s="102" t="s">
         <v>3919</v>
-      </c>
-      <c r="E176" s="102" t="s">
-        <v>3663</v>
       </c>
       <c r="F176" s="102" t="s">
         <v>4102</v>
@@ -24472,16 +24476,16 @@
         <v>273</v>
       </c>
       <c r="B177" s="102" t="s">
+        <v>3</v>
+      </c>
+      <c r="C177" s="102" t="s">
+        <v>3663</v>
+      </c>
+      <c r="D177" s="102" t="s">
         <v>274</v>
       </c>
-      <c r="C177" s="102" t="s">
-        <v>3</v>
-      </c>
-      <c r="D177" s="102" t="s">
+      <c r="E177" s="102" t="s">
         <v>3920</v>
-      </c>
-      <c r="E177" s="102" t="s">
-        <v>3663</v>
       </c>
       <c r="F177" s="102" t="s">
         <v>1504</v>
@@ -24504,16 +24508,16 @@
         <v>275</v>
       </c>
       <c r="B178" s="102" t="s">
+        <v>3</v>
+      </c>
+      <c r="C178" s="102" t="s">
+        <v>3663</v>
+      </c>
+      <c r="D178" s="102" t="s">
         <v>276</v>
       </c>
-      <c r="C178" s="102" t="s">
-        <v>3</v>
-      </c>
-      <c r="D178" s="102" t="s">
+      <c r="E178" s="102" t="s">
         <v>3921</v>
-      </c>
-      <c r="E178" s="102" t="s">
-        <v>3663</v>
       </c>
       <c r="F178" s="102" t="s">
         <v>2495</v>

--- a/doc/excel/認証タスク.xlsx
+++ b/doc/excel/認証タスク.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/suepie/Develop/10_project/aws-atuh-poc/doc/excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1FEDE968-6C9E-5346-B573-0EB3D7C65F34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{477B5B2B-68EE-8845-B11A-B4A1EAF69991}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="780" windowWidth="34200" windowHeight="21460" activeTab="3" xr2:uid="{B021B529-7D79-6D49-8055-5FE1DF3A55F9}"/>
   </bookViews>

--- a/doc/excel/認証タスク.xlsx
+++ b/doc/excel/認証タスク.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/suepie/Develop/10_project/aws-atuh-poc/doc/excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34AF9F1B-95E9-6545-A7CB-804813093C1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69AB6460-EEEA-FD49-9F69-88C10FCEEF79}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="780" windowWidth="34200" windowHeight="21460" firstSheet="1" activeTab="4" xr2:uid="{B021B529-7D79-6D49-8055-5FE1DF3A55F9}"/>
   </bookViews>
